--- a/01_Input/00_CO Validation/Mauritius - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Mauritius - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27016"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="350" documentId="11_22A4E67450481778D11D2BA3F348756C7829339C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77F5B9DB-C42F-47BE-908C-51476CDCF179}"/>
+  <xr:revisionPtr revIDLastSave="382" documentId="11_22A4E67450481778D11D2BA3F348756C7829339C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A904EC2D-5628-413B-9A00-A84CB28D3C13}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,6 +15,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="109">
   <si>
     <t>Project ID</t>
   </si>
@@ -202,6 +205,9 @@
   <si>
     <t xml:space="preserve">Based on estimate of low-emission MW divided by effective capacity of the power system, multiplied by total number of households/household composition in Mauritius and Rodrigues.
 Installation of rooftopps solar PV panels in households is ongoing. </t>
+  </si>
+  <si>
+    <t>Energy Storage (MW)</t>
   </si>
   <si>
     <t>Battery energy storage system procured MW</t>
@@ -575,7 +581,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -663,12 +669,87 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -785,14 +866,86 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -813,18 +966,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1131,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1EA8529-86F5-4E00-BF5D-B1BB315D4BA2}">
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="66.28515625" bestFit="1" customWidth="1"/>
@@ -1143,17 +1284,17 @@
     <col min="13" max="13" width="56.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:19">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="48" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="14" t="s">
@@ -1171,13 +1312,13 @@
       <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="42" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="42" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="12" t="s">
@@ -1201,22 +1342,21 @@
       <c r="S1" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="42"/>
-    </row>
-    <row r="2" spans="1:20" ht="60.75">
-      <c r="A2" s="45">
+    </row>
+    <row r="2" spans="1:19" ht="60.75">
+      <c r="A2" s="52">
         <v>6486</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="50">
         <v>5600607</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="46" t="s">
         <v>21</v>
       </c>
       <c r="F2" s="15" t="s">
@@ -1228,31 +1368,30 @@
       <c r="H2" s="8">
         <v>0.75</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="53" t="s">
+      <c r="J2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="17"/>
-      <c r="L2" s="25" t="s">
+      <c r="K2" s="65"/>
+      <c r="L2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="35"/>
+      <c r="M2" s="65"/>
       <c r="N2" s="17"/>
       <c r="O2" s="17"/>
       <c r="P2" s="17"/>
       <c r="Q2" s="17"/>
       <c r="R2" s="17"/>
       <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-    </row>
-    <row r="3" spans="1:20" ht="152.25">
-      <c r="A3" s="45"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="22" t="s">
+    </row>
+    <row r="3" spans="1:19" ht="152.25">
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="47" t="s">
         <v>26</v>
       </c>
       <c r="F3" s="23" t="s">
@@ -1264,13 +1403,17 @@
       <c r="H3" s="24">
         <v>700000</v>
       </c>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="53"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="36" t="s">
+      <c r="J3" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="65"/>
+      <c r="L3" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="66" t="s">
         <v>29</v>
       </c>
       <c r="N3" s="17"/>
@@ -1279,14 +1422,13 @@
       <c r="Q3" s="17"/>
       <c r="R3" s="17"/>
       <c r="S3" s="17"/>
-      <c r="T3" s="17"/>
-    </row>
-    <row r="4" spans="1:20" ht="106.5">
-      <c r="A4" s="45"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="9" t="s">
+    </row>
+    <row r="4" spans="1:19" ht="106.5">
+      <c r="A4" s="53"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="46" t="s">
         <v>30</v>
       </c>
       <c r="F4" s="9" t="s">
@@ -1298,27 +1440,30 @@
       <c r="H4" s="8">
         <v>1</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="53"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="37"/>
+      <c r="J4" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="65"/>
+      <c r="L4" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="67"/>
       <c r="N4" s="17"/>
       <c r="O4" s="17"/>
       <c r="P4" s="17"/>
       <c r="Q4" s="17"/>
       <c r="R4" s="17"/>
       <c r="S4" s="17"/>
-      <c r="T4" s="17"/>
-    </row>
-    <row r="5" spans="1:20" ht="60.75">
-      <c r="A5" s="45"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="9" t="s">
+    </row>
+    <row r="5" spans="1:19" ht="60.75">
+      <c r="A5" s="53"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="46" t="s">
         <v>33</v>
       </c>
       <c r="F5" s="10" t="s">
@@ -1330,35 +1475,38 @@
       <c r="H5" s="8">
         <v>21000</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="53"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="37"/>
+      <c r="J5" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="65"/>
+      <c r="L5" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="67"/>
       <c r="N5" s="17"/>
       <c r="O5" s="17"/>
       <c r="P5" s="17"/>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
       <c r="S5" s="17"/>
-      <c r="T5" s="17"/>
-    </row>
-    <row r="6" spans="1:20" ht="148.5" customHeight="1">
-      <c r="A6" s="25">
+    </row>
+    <row r="6" spans="1:19" ht="148.5" customHeight="1">
+      <c r="A6" s="52">
         <v>5681</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="50">
         <v>28210000</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="61" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="5" t="s">
@@ -1373,11 +1521,11 @@
       <c r="I6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="54" t="s">
+      <c r="J6" s="45" t="s">
         <v>42</v>
       </c>
       <c r="K6" s="17"/>
-      <c r="L6" s="25" t="s">
+      <c r="L6" s="49" t="s">
         <v>25</v>
       </c>
       <c r="M6" s="37"/>
@@ -1387,14 +1535,13 @@
       <c r="Q6" s="17"/>
       <c r="R6" s="17"/>
       <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-    </row>
-    <row r="7" spans="1:20" ht="151.5" customHeight="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="5" t="s">
+    </row>
+    <row r="7" spans="1:19" ht="151.5" customHeight="1">
+      <c r="A7" s="53"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="61" t="s">
         <v>43</v>
       </c>
       <c r="F7" s="5" t="s">
@@ -1409,9 +1556,13 @@
       <c r="I7" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="55"/>
+      <c r="J7" s="45" t="s">
+        <v>42</v>
+      </c>
       <c r="K7" s="17"/>
-      <c r="L7" s="25"/>
+      <c r="L7" s="49" t="s">
+        <v>25</v>
+      </c>
       <c r="M7" s="37"/>
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
@@ -1419,14 +1570,13 @@
       <c r="Q7" s="17"/>
       <c r="R7" s="17"/>
       <c r="S7" s="17"/>
-      <c r="T7" s="17"/>
-    </row>
-    <row r="8" spans="1:20" ht="105" customHeight="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="5" t="s">
+    </row>
+    <row r="8" spans="1:19" ht="105" customHeight="1">
+      <c r="A8" s="53"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="61" t="s">
         <v>39</v>
       </c>
       <c r="F8" s="5" t="s">
@@ -1441,9 +1591,13 @@
       <c r="I8" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="55"/>
+      <c r="J8" s="45" t="s">
+        <v>42</v>
+      </c>
       <c r="K8" s="17"/>
-      <c r="L8" s="25"/>
+      <c r="L8" s="49" t="s">
+        <v>25</v>
+      </c>
       <c r="M8" s="37"/>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
@@ -1451,29 +1605,33 @@
       <c r="Q8" s="17"/>
       <c r="R8" s="17"/>
       <c r="S8" s="17"/>
-      <c r="T8" s="17"/>
-    </row>
-    <row r="9" spans="1:20" ht="147.75" customHeight="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="5"/>
+    </row>
+    <row r="9" spans="1:19" ht="147.75" customHeight="1">
+      <c r="A9" s="53"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="E9" s="51" t="s">
+        <v>50</v>
+      </c>
       <c r="F9" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" s="5">
         <v>18</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="55"/>
+        <v>53</v>
+      </c>
+      <c r="J9" s="45" t="s">
+        <v>42</v>
+      </c>
       <c r="K9" s="17"/>
-      <c r="L9" s="25"/>
+      <c r="L9" s="49" t="s">
+        <v>25</v>
+      </c>
       <c r="M9" s="37"/>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
@@ -1481,29 +1639,32 @@
       <c r="Q9" s="17"/>
       <c r="R9" s="17"/>
       <c r="S9" s="17"/>
-      <c r="T9" s="17"/>
-    </row>
-    <row r="10" spans="1:20" ht="86.25" customHeight="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="5" t="s">
+    </row>
+    <row r="10" spans="1:19" ht="86.25" customHeight="1">
+      <c r="A10" s="53"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="61" t="s">
         <v>30</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J10" s="55"/>
+        <v>56</v>
+      </c>
+      <c r="J10" s="45" t="s">
+        <v>42</v>
+      </c>
       <c r="K10" s="17"/>
-      <c r="L10" s="25"/>
+      <c r="L10" s="49" t="s">
+        <v>25</v>
+      </c>
       <c r="M10" s="38"/>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
@@ -1511,18 +1672,17 @@
       <c r="Q10" s="17"/>
       <c r="R10" s="17"/>
       <c r="S10" s="17"/>
-      <c r="T10" s="17"/>
-    </row>
-    <row r="11" spans="1:20" ht="262.5" customHeight="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="5" t="s">
+    </row>
+    <row r="11" spans="1:19" ht="262.5" customHeight="1">
+      <c r="A11" s="54"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="61" t="s">
         <v>21</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" s="5">
         <v>5</v>
@@ -1531,13 +1691,17 @@
         <v>11</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="56"/>
+        <v>58</v>
+      </c>
+      <c r="J11" s="45" t="s">
+        <v>42</v>
+      </c>
       <c r="K11" s="17"/>
-      <c r="L11" s="25"/>
+      <c r="L11" s="49" t="s">
+        <v>25</v>
+      </c>
       <c r="M11" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
@@ -1545,26 +1709,25 @@
       <c r="Q11" s="17"/>
       <c r="R11" s="17"/>
       <c r="S11" s="17"/>
-      <c r="T11" s="17"/>
-    </row>
-    <row r="12" spans="1:20" ht="106.5">
-      <c r="A12" s="25">
+    </row>
+    <row r="12" spans="1:19" ht="106.5">
+      <c r="A12" s="51">
         <v>5509</v>
       </c>
-      <c r="B12" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="25">
+      <c r="B12" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="51">
         <v>4532164</v>
       </c>
-      <c r="E12" s="18" t="s">
-        <v>60</v>
+      <c r="E12" s="60" t="s">
+        <v>61</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12" s="19">
         <v>4</v>
@@ -1573,9 +1736,9 @@
         <v>40</v>
       </c>
       <c r="I12" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="J12" s="54" t="s">
+        <v>63</v>
+      </c>
+      <c r="J12" s="44" t="s">
         <v>24</v>
       </c>
       <c r="K12" s="17"/>
@@ -1583,7 +1746,7 @@
         <v>25</v>
       </c>
       <c r="M12" s="40" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N12" s="17"/>
       <c r="O12" s="17"/>
@@ -1591,18 +1754,17 @@
       <c r="Q12" s="17"/>
       <c r="R12" s="17"/>
       <c r="S12" s="17"/>
-      <c r="T12" s="17"/>
-    </row>
-    <row r="13" spans="1:20" ht="30.75">
-      <c r="A13" s="25"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="18" t="s">
-        <v>64</v>
+    </row>
+    <row r="13" spans="1:19" ht="30.75">
+      <c r="A13" s="51"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="60" t="s">
+        <v>65</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G13" s="19">
         <v>0</v>
@@ -1611,13 +1773,17 @@
         <v>435</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" s="55"/>
+        <v>67</v>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>24</v>
+      </c>
       <c r="K13" s="17"/>
-      <c r="L13" s="25"/>
+      <c r="L13" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="M13" s="41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N13" s="17"/>
       <c r="O13" s="17"/>
@@ -1625,18 +1791,17 @@
       <c r="Q13" s="17"/>
       <c r="R13" s="17"/>
       <c r="S13" s="17"/>
-      <c r="T13" s="17"/>
-    </row>
-    <row r="14" spans="1:20" ht="45.75">
-      <c r="A14" s="25"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="18" t="s">
-        <v>64</v>
+    </row>
+    <row r="14" spans="1:19" ht="45.75">
+      <c r="A14" s="51"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="60" t="s">
+        <v>65</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14" s="19">
         <v>0</v>
@@ -1645,11 +1810,15 @@
         <v>170</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="J14" s="55"/>
+        <v>69</v>
+      </c>
+      <c r="J14" s="44" t="s">
+        <v>24</v>
+      </c>
       <c r="K14" s="17"/>
-      <c r="L14" s="25"/>
+      <c r="L14" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="M14" s="35"/>
       <c r="N14" s="17"/>
       <c r="O14" s="17"/>
@@ -1657,31 +1826,34 @@
       <c r="Q14" s="17"/>
       <c r="R14" s="17"/>
       <c r="S14" s="17"/>
-      <c r="T14" s="17"/>
-    </row>
-    <row r="15" spans="1:20" ht="76.5">
-      <c r="A15" s="25"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="18" t="s">
-        <v>69</v>
+    </row>
+    <row r="15" spans="1:19" ht="76.5">
+      <c r="A15" s="51"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="60" t="s">
+        <v>70</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15" s="34"/>
       <c r="H15" s="34">
         <v>31</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J15" s="55"/>
+        <v>72</v>
+      </c>
+      <c r="J15" s="44" t="s">
+        <v>24</v>
+      </c>
       <c r="K15" s="33">
         <v>0.33</v>
       </c>
-      <c r="L15" s="25"/>
+      <c r="L15" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="M15" s="35"/>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
@@ -1689,18 +1861,17 @@
       <c r="Q15" s="17"/>
       <c r="R15" s="17"/>
       <c r="S15" s="17"/>
-      <c r="T15" s="17"/>
-    </row>
-    <row r="16" spans="1:20" ht="81">
-      <c r="A16" s="25"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="18" t="s">
+    </row>
+    <row r="16" spans="1:19" ht="81">
+      <c r="A16" s="51"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="60" t="s">
         <v>30</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -1709,11 +1880,15 @@
         <v>50</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="J16" s="55"/>
+        <v>74</v>
+      </c>
+      <c r="J16" s="44" t="s">
+        <v>24</v>
+      </c>
       <c r="K16" s="17"/>
-      <c r="L16" s="25"/>
+      <c r="L16" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="M16" s="35"/>
       <c r="N16" s="17"/>
       <c r="O16" s="17"/>
@@ -1721,18 +1896,17 @@
       <c r="Q16" s="17"/>
       <c r="R16" s="17"/>
       <c r="S16" s="17"/>
-      <c r="T16" s="17"/>
-    </row>
-    <row r="17" spans="1:20" ht="76.5">
-      <c r="A17" s="25"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="18" t="s">
+    </row>
+    <row r="17" spans="1:19" ht="76.5">
+      <c r="A17" s="51"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="60" t="s">
         <v>30</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -1741,11 +1915,15 @@
         <v>14</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="J17" s="55"/>
+        <v>76</v>
+      </c>
+      <c r="J17" s="44" t="s">
+        <v>24</v>
+      </c>
       <c r="K17" s="17"/>
-      <c r="L17" s="25"/>
+      <c r="L17" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="M17" s="35"/>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
@@ -1753,18 +1931,17 @@
       <c r="Q17" s="17"/>
       <c r="R17" s="17"/>
       <c r="S17" s="17"/>
-      <c r="T17" s="17"/>
-    </row>
-    <row r="18" spans="1:20" ht="106.5">
-      <c r="A18" s="25"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="18" t="s">
-        <v>60</v>
+    </row>
+    <row r="18" spans="1:19" ht="106.5">
+      <c r="A18" s="49"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="60" t="s">
+        <v>61</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G18" s="19">
         <v>108</v>
@@ -1772,12 +1949,16 @@
       <c r="H18" s="19">
         <v>348</v>
       </c>
-      <c r="I18" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="J18" s="56"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="25"/>
+      <c r="I18" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="J18" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="64"/>
+      <c r="L18" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="M18" s="35"/>
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
@@ -1785,12 +1966,8 @@
       <c r="Q18" s="17"/>
       <c r="R18" s="17"/>
       <c r="S18" s="17"/>
-      <c r="T18" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:A5"/>
-  </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5 E7" xr:uid="{ACE05F1D-CAE5-4EDA-A504-3E8FC4C61FB0}"/>
   </dataValidations>
@@ -1890,7 +2067,7 @@
       <c r="T1" s="42"/>
     </row>
     <row r="2" spans="1:20" ht="60.75">
-      <c r="A2" s="45">
+      <c r="A2" s="69">
         <v>6486</v>
       </c>
       <c r="B2" s="25" t="s">
@@ -1917,11 +2094,11 @@
       <c r="I2" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="43" t="s">
+      <c r="J2" s="70" t="s">
         <v>24</v>
       </c>
       <c r="K2" s="17"/>
-      <c r="L2" s="44" t="s">
+      <c r="L2" s="71" t="s">
         <v>25</v>
       </c>
       <c r="M2" s="35"/>
@@ -1934,7 +2111,7 @@
       <c r="T2" s="17"/>
     </row>
     <row r="3" spans="1:20" ht="152.25">
-      <c r="A3" s="45"/>
+      <c r="A3" s="69"/>
       <c r="B3" s="25"/>
       <c r="C3" s="25"/>
       <c r="D3" s="25"/>
@@ -1953,9 +2130,9 @@
       <c r="I3" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="43"/>
+      <c r="J3" s="70"/>
       <c r="K3" s="17"/>
-      <c r="L3" s="44"/>
+      <c r="L3" s="71"/>
       <c r="M3" s="36" t="s">
         <v>29</v>
       </c>
@@ -1968,7 +2145,7 @@
       <c r="T3" s="17"/>
     </row>
     <row r="4" spans="1:20" ht="106.5">
-      <c r="A4" s="45"/>
+      <c r="A4" s="69"/>
       <c r="B4" s="25"/>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
@@ -1987,9 +2164,9 @@
       <c r="I4" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="43"/>
+      <c r="J4" s="70"/>
       <c r="K4" s="17"/>
-      <c r="L4" s="44"/>
+      <c r="L4" s="71"/>
       <c r="M4" s="37"/>
       <c r="N4" s="17"/>
       <c r="O4" s="17"/>
@@ -2000,7 +2177,7 @@
       <c r="T4" s="17"/>
     </row>
     <row r="5" spans="1:20" ht="60.75">
-      <c r="A5" s="45"/>
+      <c r="A5" s="69"/>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
@@ -2019,9 +2196,9 @@
       <c r="I5" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="43"/>
+      <c r="J5" s="70"/>
       <c r="K5" s="17"/>
-      <c r="L5" s="44"/>
+      <c r="L5" s="71"/>
       <c r="M5" s="37"/>
       <c r="N5" s="17"/>
       <c r="O5" s="17"/>
@@ -2059,11 +2236,11 @@
       <c r="I6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="46" t="s">
+      <c r="J6" s="72" t="s">
         <v>42</v>
       </c>
       <c r="K6" s="17"/>
-      <c r="L6" s="45" t="s">
+      <c r="L6" s="69" t="s">
         <v>25</v>
       </c>
       <c r="M6" s="37"/>
@@ -2095,9 +2272,9 @@
       <c r="I7" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="47"/>
+      <c r="J7" s="73"/>
       <c r="K7" s="17"/>
-      <c r="L7" s="45"/>
+      <c r="L7" s="69"/>
       <c r="M7" s="37"/>
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
@@ -2127,9 +2304,9 @@
       <c r="I8" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="47"/>
+      <c r="J8" s="73"/>
       <c r="K8" s="17"/>
-      <c r="L8" s="45"/>
+      <c r="L8" s="69"/>
       <c r="M8" s="37"/>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
@@ -2146,20 +2323,20 @@
       <c r="D9" s="25"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" s="5">
         <v>18</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="47"/>
+        <v>53</v>
+      </c>
+      <c r="J9" s="73"/>
       <c r="K9" s="17"/>
-      <c r="L9" s="45"/>
+      <c r="L9" s="69"/>
       <c r="M9" s="37"/>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
@@ -2178,18 +2355,18 @@
         <v>30</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J10" s="47"/>
+        <v>56</v>
+      </c>
+      <c r="J10" s="73"/>
       <c r="K10" s="17"/>
-      <c r="L10" s="45"/>
+      <c r="L10" s="69"/>
       <c r="M10" s="38"/>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
@@ -2208,7 +2385,7 @@
         <v>21</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" s="5">
         <v>5</v>
@@ -2217,13 +2394,13 @@
         <v>11</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="48"/>
+        <v>58</v>
+      </c>
+      <c r="J11" s="74"/>
       <c r="K11" s="17"/>
-      <c r="L11" s="45"/>
+      <c r="L11" s="69"/>
       <c r="M11" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
@@ -2238,19 +2415,19 @@
         <v>5509</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D12" s="25">
         <v>4532164</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12" s="19">
         <v>4</v>
@@ -2259,15 +2436,15 @@
         <v>40</v>
       </c>
       <c r="I12" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="J12" s="46" t="s">
+        <v>63</v>
+      </c>
+      <c r="J12" s="72" t="s">
         <v>24</v>
       </c>
       <c r="K12" s="17"/>
-      <c r="L12" s="45"/>
+      <c r="L12" s="69"/>
       <c r="M12" s="40" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N12" s="17"/>
       <c r="O12" s="17"/>
@@ -2283,10 +2460,10 @@
       <c r="C13" s="31"/>
       <c r="D13" s="25"/>
       <c r="E13" s="18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G13" s="19">
         <v>0</v>
@@ -2295,13 +2472,13 @@
         <v>435</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" s="47"/>
+        <v>67</v>
+      </c>
+      <c r="J13" s="73"/>
       <c r="K13" s="17"/>
-      <c r="L13" s="45"/>
+      <c r="L13" s="69"/>
       <c r="M13" s="41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N13" s="17"/>
       <c r="O13" s="17"/>
@@ -2317,10 +2494,10 @@
       <c r="C14" s="31"/>
       <c r="D14" s="25"/>
       <c r="E14" s="18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14" s="19">
         <v>0</v>
@@ -2329,11 +2506,11 @@
         <v>170</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="J14" s="47"/>
+        <v>69</v>
+      </c>
+      <c r="J14" s="73"/>
       <c r="K14" s="17"/>
-      <c r="L14" s="45"/>
+      <c r="L14" s="69"/>
       <c r="M14" s="35"/>
       <c r="N14" s="17"/>
       <c r="O14" s="17"/>
@@ -2349,23 +2526,23 @@
       <c r="C15" s="31"/>
       <c r="D15" s="25"/>
       <c r="E15" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15" s="34">
         <v>31</v>
       </c>
       <c r="H15" s="34"/>
       <c r="I15" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J15" s="47"/>
+        <v>72</v>
+      </c>
+      <c r="J15" s="73"/>
       <c r="K15" s="33">
         <v>0.33</v>
       </c>
-      <c r="L15" s="45"/>
+      <c r="L15" s="69"/>
       <c r="M15" s="35"/>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
@@ -2384,7 +2561,7 @@
         <v>30</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -2393,11 +2570,11 @@
         <v>50</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="J16" s="47"/>
+        <v>74</v>
+      </c>
+      <c r="J16" s="73"/>
       <c r="K16" s="17"/>
-      <c r="L16" s="45"/>
+      <c r="L16" s="69"/>
       <c r="M16" s="35"/>
       <c r="N16" s="17"/>
       <c r="O16" s="17"/>
@@ -2416,7 +2593,7 @@
         <v>30</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -2425,11 +2602,11 @@
         <v>14</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="J17" s="47"/>
+        <v>76</v>
+      </c>
+      <c r="J17" s="73"/>
       <c r="K17" s="17"/>
-      <c r="L17" s="45"/>
+      <c r="L17" s="69"/>
       <c r="M17" s="35"/>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
@@ -2445,10 +2622,10 @@
       <c r="C18" s="32"/>
       <c r="D18" s="25"/>
       <c r="E18" s="18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G18" s="19">
         <v>108</v>
@@ -2457,11 +2634,11 @@
         <v>348</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="J18" s="48"/>
+        <v>78</v>
+      </c>
+      <c r="J18" s="74"/>
       <c r="K18" s="17"/>
-      <c r="L18" s="45"/>
+      <c r="L18" s="69"/>
       <c r="M18" s="35"/>
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
@@ -2579,7 +2756,7 @@
       <c r="T1" s="42"/>
     </row>
     <row r="2" spans="1:20" ht="60.75">
-      <c r="A2" s="45">
+      <c r="A2" s="69">
         <v>6486</v>
       </c>
       <c r="B2" s="25" t="s">
@@ -2606,11 +2783,11 @@
       <c r="I2" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="43" t="s">
+      <c r="J2" s="70" t="s">
         <v>24</v>
       </c>
       <c r="K2" s="17"/>
-      <c r="L2" s="44" t="s">
+      <c r="L2" s="71" t="s">
         <v>25</v>
       </c>
       <c r="M2" s="35"/>
@@ -2623,7 +2800,7 @@
       <c r="T2" s="17"/>
     </row>
     <row r="3" spans="1:20" ht="152.25">
-      <c r="A3" s="45"/>
+      <c r="A3" s="69"/>
       <c r="B3" s="25"/>
       <c r="C3" s="25"/>
       <c r="D3" s="25"/>
@@ -2642,9 +2819,9 @@
       <c r="I3" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="43"/>
+      <c r="J3" s="70"/>
       <c r="K3" s="17"/>
-      <c r="L3" s="44"/>
+      <c r="L3" s="71"/>
       <c r="M3" s="36" t="s">
         <v>29</v>
       </c>
@@ -2657,7 +2834,7 @@
       <c r="T3" s="17"/>
     </row>
     <row r="4" spans="1:20" ht="106.5">
-      <c r="A4" s="45"/>
+      <c r="A4" s="69"/>
       <c r="B4" s="25"/>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
@@ -2676,9 +2853,9 @@
       <c r="I4" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="43"/>
+      <c r="J4" s="70"/>
       <c r="K4" s="17"/>
-      <c r="L4" s="44"/>
+      <c r="L4" s="71"/>
       <c r="M4" s="37"/>
       <c r="N4" s="17"/>
       <c r="O4" s="17"/>
@@ -2689,7 +2866,7 @@
       <c r="T4" s="17"/>
     </row>
     <row r="5" spans="1:20" ht="60.75">
-      <c r="A5" s="45"/>
+      <c r="A5" s="69"/>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
@@ -2708,9 +2885,9 @@
       <c r="I5" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="43"/>
+      <c r="J5" s="70"/>
       <c r="K5" s="17"/>
-      <c r="L5" s="44"/>
+      <c r="L5" s="71"/>
       <c r="M5" s="37"/>
       <c r="N5" s="17"/>
       <c r="O5" s="17"/>
@@ -2748,11 +2925,11 @@
       <c r="I6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="46" t="s">
+      <c r="J6" s="72" t="s">
         <v>42</v>
       </c>
       <c r="K6" s="17"/>
-      <c r="L6" s="45" t="s">
+      <c r="L6" s="69" t="s">
         <v>25</v>
       </c>
       <c r="M6" s="37"/>
@@ -2784,9 +2961,9 @@
       <c r="I7" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="47"/>
+      <c r="J7" s="73"/>
       <c r="K7" s="17"/>
-      <c r="L7" s="45"/>
+      <c r="L7" s="69"/>
       <c r="M7" s="37"/>
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
@@ -2816,9 +2993,9 @@
       <c r="I8" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="47"/>
+      <c r="J8" s="73"/>
       <c r="K8" s="17"/>
-      <c r="L8" s="45"/>
+      <c r="L8" s="69"/>
       <c r="M8" s="37"/>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
@@ -2835,20 +3012,20 @@
       <c r="D9" s="25"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" s="5">
         <v>18</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="47"/>
+        <v>53</v>
+      </c>
+      <c r="J9" s="73"/>
       <c r="K9" s="17"/>
-      <c r="L9" s="45"/>
+      <c r="L9" s="69"/>
       <c r="M9" s="37"/>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
@@ -2867,18 +3044,18 @@
         <v>30</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J10" s="47"/>
+        <v>56</v>
+      </c>
+      <c r="J10" s="73"/>
       <c r="K10" s="17"/>
-      <c r="L10" s="45"/>
+      <c r="L10" s="69"/>
       <c r="M10" s="38"/>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
@@ -2897,7 +3074,7 @@
         <v>21</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" s="5">
         <v>5</v>
@@ -2906,13 +3083,13 @@
         <v>11</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="48"/>
+        <v>58</v>
+      </c>
+      <c r="J11" s="74"/>
       <c r="K11" s="17"/>
-      <c r="L11" s="45"/>
+      <c r="L11" s="69"/>
       <c r="M11" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
@@ -2927,19 +3104,19 @@
         <v>5509</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D12" s="25">
         <v>4532164</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12" s="19">
         <v>4</v>
@@ -2948,15 +3125,15 @@
         <v>40</v>
       </c>
       <c r="I12" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="J12" s="46" t="s">
+        <v>63</v>
+      </c>
+      <c r="J12" s="72" t="s">
         <v>24</v>
       </c>
       <c r="K12" s="17"/>
-      <c r="L12" s="45"/>
+      <c r="L12" s="69"/>
       <c r="M12" s="40" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N12" s="17"/>
       <c r="O12" s="17"/>
@@ -2972,10 +3149,10 @@
       <c r="C13" s="31"/>
       <c r="D13" s="25"/>
       <c r="E13" s="18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G13" s="19">
         <v>0</v>
@@ -2984,13 +3161,13 @@
         <v>435</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" s="47"/>
+        <v>67</v>
+      </c>
+      <c r="J13" s="73"/>
       <c r="K13" s="17"/>
-      <c r="L13" s="45"/>
+      <c r="L13" s="69"/>
       <c r="M13" s="41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N13" s="17"/>
       <c r="O13" s="17"/>
@@ -3006,10 +3183,10 @@
       <c r="C14" s="31"/>
       <c r="D14" s="25"/>
       <c r="E14" s="18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14" s="19">
         <v>0</v>
@@ -3018,11 +3195,11 @@
         <v>170</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="J14" s="47"/>
+        <v>69</v>
+      </c>
+      <c r="J14" s="73"/>
       <c r="K14" s="17"/>
-      <c r="L14" s="45"/>
+      <c r="L14" s="69"/>
       <c r="M14" s="35"/>
       <c r="N14" s="17"/>
       <c r="O14" s="17"/>
@@ -3038,23 +3215,23 @@
       <c r="C15" s="31"/>
       <c r="D15" s="25"/>
       <c r="E15" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15" s="34">
         <v>31</v>
       </c>
       <c r="H15" s="34"/>
       <c r="I15" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J15" s="47"/>
+        <v>72</v>
+      </c>
+      <c r="J15" s="73"/>
       <c r="K15" s="33">
         <v>0.33</v>
       </c>
-      <c r="L15" s="45"/>
+      <c r="L15" s="69"/>
       <c r="M15" s="35"/>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
@@ -3073,7 +3250,7 @@
         <v>30</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -3082,11 +3259,11 @@
         <v>50</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="J16" s="47"/>
+        <v>74</v>
+      </c>
+      <c r="J16" s="73"/>
       <c r="K16" s="17"/>
-      <c r="L16" s="45"/>
+      <c r="L16" s="69"/>
       <c r="M16" s="35"/>
       <c r="N16" s="17"/>
       <c r="O16" s="17"/>
@@ -3105,7 +3282,7 @@
         <v>30</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -3114,11 +3291,11 @@
         <v>14</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="J17" s="47"/>
+        <v>76</v>
+      </c>
+      <c r="J17" s="73"/>
       <c r="K17" s="17"/>
-      <c r="L17" s="45"/>
+      <c r="L17" s="69"/>
       <c r="M17" s="35"/>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
@@ -3134,10 +3311,10 @@
       <c r="C18" s="32"/>
       <c r="D18" s="25"/>
       <c r="E18" s="18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G18" s="19">
         <v>108</v>
@@ -3146,11 +3323,11 @@
         <v>348</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="J18" s="48"/>
+        <v>78</v>
+      </c>
+      <c r="J18" s="74"/>
       <c r="K18" s="17"/>
-      <c r="L18" s="45"/>
+      <c r="L18" s="69"/>
       <c r="M18" s="35"/>
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
@@ -3203,160 +3380,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="49" t="s">
-        <v>80</v>
+      <c r="A2" s="75" t="s">
+        <v>81</v>
       </c>
       <c r="B2" t="s">
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="49"/>
+      <c r="A3" s="75"/>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="49"/>
+      <c r="A4" s="75"/>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="50" t="s">
-        <v>85</v>
+      <c r="A5" s="76" t="s">
+        <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="50"/>
+      <c r="A6" s="76"/>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="50"/>
+      <c r="A7" s="76"/>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="50"/>
+      <c r="A8" s="76"/>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="50"/>
+      <c r="A9" s="76"/>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="51" t="s">
-        <v>96</v>
+      <c r="A10" s="77" t="s">
+        <v>97</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="51"/>
+      <c r="A11" s="77"/>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="52" t="s">
-        <v>99</v>
+      <c r="A12" s="78" t="s">
+        <v>100</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="52"/>
+      <c r="A13" s="78"/>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="52"/>
+      <c r="A14" s="78"/>
       <c r="B14" t="s">
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B15" t="s">
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/01_Input/00_CO Validation/Mauritius - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Mauritius - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27016"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27109"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="382" documentId="11_22A4E67450481778D11D2BA3F348756C7829339C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A904EC2D-5628-413B-9A00-A84CB28D3C13}"/>
+  <xr:revisionPtr revIDLastSave="397" documentId="11_22A4E67450481778D11D2BA3F348756C7829339C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDAD8C55-CC1D-46C0-86D5-96E6996E7348}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="114">
   <si>
     <t>Project ID</t>
   </si>
@@ -84,6 +84,9 @@
     <t>RISE Taxonomy</t>
   </si>
   <si>
+    <t>Impact Tier</t>
+  </si>
+  <si>
     <t>Flagship</t>
   </si>
   <si>
@@ -112,6 +115,9 @@
   </si>
   <si>
     <t>VF</t>
+  </si>
+  <si>
+    <t>Renewable Energy</t>
   </si>
   <si>
     <t>Campaign Participant</t>
@@ -153,6 +159,9 @@
     <t>Approved Gender-responsive Policy and Regulatory Framework documents endorsed and approved by the Cabinet/Parliament</t>
   </si>
   <si>
+    <t>Tier 2</t>
+  </si>
+  <si>
     <t>Transport Services</t>
   </si>
   <si>
@@ -228,6 +237,9 @@
   </si>
   <si>
     <t>Government is fully supporting the project and is maintaining policy of promoting renewable energy. As a result, the Mauritius Renewable Energy Agency (MARENA) is in place and is functioning under the aegis of the Ministry of Energy and Public Utilities.</t>
+  </si>
+  <si>
+    <t>Tier 1</t>
   </si>
   <si>
     <t>Actual MW installed by category</t>
@@ -292,6 +304,9 @@
       <t>Project ID: 5509
 Project Title:Realising  Energy Savings and Climate Benefits of implementing Mandatory EEnergy Auditing in the Republic of Mauritius</t>
     </r>
+  </si>
+  <si>
+    <t>Energy Efficiency</t>
   </si>
   <si>
     <t>Small Enterprises</t>
@@ -507,7 +522,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -577,6 +592,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -749,7 +770,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -866,78 +887,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -966,6 +915,145 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1272,7 +1360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1EA8529-86F5-4E00-BF5D-B1BB315D4BA2}">
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="66.28515625" bestFit="1" customWidth="1"/>
@@ -1282,694 +1370,762 @@
     <col min="8" max="8" width="19.5703125" style="4" customWidth="1"/>
     <col min="9" max="9" width="50.85546875" customWidth="1"/>
     <col min="13" max="13" width="56.5703125" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:20">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="48" t="s">
+      <c r="C1" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="48" t="s">
+      <c r="D1" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="42" t="s">
+      <c r="J1" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="42" t="s">
+      <c r="L1" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="42" t="s">
+      <c r="N1" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="42" t="s">
+      <c r="O1" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="42" t="s">
+      <c r="P1" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="42" t="s">
+      <c r="Q1" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="42" t="s">
+      <c r="R1" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="42" t="s">
+      <c r="S1" s="56" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" ht="60.75">
-      <c r="A2" s="52">
+      <c r="T1" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="60.75">
+      <c r="A2" s="59">
         <v>6486</v>
       </c>
-      <c r="B2" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="55" t="s">
+      <c r="B2" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="50">
+      <c r="C2" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="61">
         <v>5600607</v>
       </c>
-      <c r="E2" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="15" t="s">
+      <c r="E2" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="8">
+      <c r="F2" s="63" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="64">
         <v>0</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="64">
         <v>0.75</v>
       </c>
-      <c r="I2" s="62" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="44" t="s">
+      <c r="I2" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="65"/>
-      <c r="L2" s="49" t="s">
+      <c r="J2" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="65"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="17"/>
-    </row>
-    <row r="3" spans="1:19" ht="152.25">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="47" t="s">
+      <c r="K2" s="67"/>
+      <c r="L2" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="M2" s="67"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="24">
+      <c r="Q2" s="70"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
+    </row>
+    <row r="3" spans="1:20" ht="152.25">
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="73" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="64">
         <v>0</v>
       </c>
-      <c r="H3" s="24">
+      <c r="H3" s="64">
         <v>700000</v>
       </c>
-      <c r="I3" s="63" t="s">
+      <c r="I3" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="67"/>
+      <c r="L3" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="74" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="69"/>
+      <c r="O3" s="69"/>
+      <c r="P3" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="70"/>
+      <c r="R3" s="69"/>
+      <c r="S3" s="69"/>
+      <c r="T3" s="69"/>
+    </row>
+    <row r="4" spans="1:20" ht="106.5">
+      <c r="A4" s="71"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="62" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="64">
+        <v>0</v>
+      </c>
+      <c r="H4" s="64">
+        <v>1</v>
+      </c>
+      <c r="I4" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="67"/>
+      <c r="L4" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="76"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q4" s="70" t="s">
+        <v>35</v>
+      </c>
+      <c r="R4" s="69"/>
+      <c r="S4" s="69"/>
+      <c r="T4" s="69"/>
+    </row>
+    <row r="5" spans="1:20" ht="60.75">
+      <c r="A5" s="71"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="62" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="77" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="64" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="64">
+        <v>21000</v>
+      </c>
+      <c r="I5" s="65" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="78" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="67"/>
+      <c r="L5" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="76"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="70"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+    </row>
+    <row r="6" spans="1:20" ht="148.5" customHeight="1">
+      <c r="A6" s="59">
+        <v>5681</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="61">
+        <v>28210000</v>
+      </c>
+      <c r="E6" s="79" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="64">
+        <v>252178</v>
+      </c>
+      <c r="H6" s="64">
+        <v>441315</v>
+      </c>
+      <c r="I6" s="81" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="69"/>
+      <c r="L6" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" s="83"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
+      <c r="P6" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="69"/>
+      <c r="S6" s="69"/>
+      <c r="T6" s="69"/>
+    </row>
+    <row r="7" spans="1:20" ht="151.5" customHeight="1">
+      <c r="A7" s="71"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="79" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="80" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="80">
+        <v>0</v>
+      </c>
+      <c r="H7" s="64">
+        <v>196000</v>
+      </c>
+      <c r="I7" s="81" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" s="69"/>
+      <c r="L7" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="83"/>
+      <c r="N7" s="69"/>
+      <c r="O7" s="69"/>
+      <c r="P7" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="70"/>
+      <c r="R7" s="69"/>
+      <c r="S7" s="69"/>
+      <c r="T7" s="69"/>
+    </row>
+    <row r="8" spans="1:20" ht="105" customHeight="1">
+      <c r="A8" s="71"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="79" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="80" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="80" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="80" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="69"/>
+      <c r="L8" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="83"/>
+      <c r="N8" s="69"/>
+      <c r="O8" s="69"/>
+      <c r="P8" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="70"/>
+      <c r="R8" s="69"/>
+      <c r="S8" s="69"/>
+      <c r="T8" s="69"/>
+    </row>
+    <row r="9" spans="1:20" ht="147.75" customHeight="1">
+      <c r="A9" s="71"/>
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="72" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="80" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="80">
+        <v>18</v>
+      </c>
+      <c r="I9" s="81" t="s">
+        <v>56</v>
+      </c>
+      <c r="J9" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="69"/>
+      <c r="L9" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="83"/>
+      <c r="N9" s="69"/>
+      <c r="O9" s="69"/>
+      <c r="P9" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q9" s="70"/>
+      <c r="R9" s="69"/>
+      <c r="S9" s="69"/>
+      <c r="T9" s="69"/>
+    </row>
+    <row r="10" spans="1:20" ht="86.25" customHeight="1">
+      <c r="A10" s="71"/>
+      <c r="B10" s="71"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="79" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="80" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="80" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="80"/>
+      <c r="I10" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="69"/>
+      <c r="L10" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="85"/>
+      <c r="N10" s="69"/>
+      <c r="O10" s="69"/>
+      <c r="P10" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q10" s="70" t="s">
+        <v>60</v>
+      </c>
+      <c r="R10" s="69"/>
+      <c r="S10" s="69"/>
+      <c r="T10" s="69"/>
+    </row>
+    <row r="11" spans="1:20" ht="262.5" customHeight="1">
+      <c r="A11" s="86"/>
+      <c r="B11" s="86"/>
+      <c r="C11" s="86"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="80">
+        <v>5</v>
+      </c>
+      <c r="H11" s="80">
+        <v>11</v>
+      </c>
+      <c r="I11" s="81" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" s="69"/>
+      <c r="L11" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" s="87" t="s">
+        <v>63</v>
+      </c>
+      <c r="N11" s="69"/>
+      <c r="O11" s="69"/>
+      <c r="P11" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q11" s="70"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="69"/>
+      <c r="T11" s="69"/>
+    </row>
+    <row r="12" spans="1:20" ht="106.5">
+      <c r="A12" s="72">
+        <v>5509</v>
+      </c>
+      <c r="B12" s="88" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="89" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="72">
+        <v>4532164</v>
+      </c>
+      <c r="E12" s="90" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="63" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="91">
+        <v>4</v>
+      </c>
+      <c r="H12" s="91">
+        <v>40</v>
+      </c>
+      <c r="I12" s="73" t="s">
+        <v>67</v>
+      </c>
+      <c r="J12" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="69"/>
+      <c r="L12" s="92" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" s="93" t="s">
+        <v>68</v>
+      </c>
+      <c r="N12" s="69"/>
+      <c r="O12" s="69"/>
+      <c r="P12" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q12" s="70"/>
+      <c r="R12" s="69"/>
+      <c r="S12" s="69"/>
+      <c r="T12" s="69"/>
+    </row>
+    <row r="13" spans="1:20" ht="30.75">
+      <c r="A13" s="72"/>
+      <c r="B13" s="88"/>
+      <c r="C13" s="89"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="90" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="91">
+        <v>0</v>
+      </c>
+      <c r="H13" s="91">
+        <v>435</v>
+      </c>
+      <c r="I13" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="J13" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" s="69"/>
+      <c r="L13" s="92" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" s="94" t="s">
+        <v>73</v>
+      </c>
+      <c r="N13" s="69"/>
+      <c r="O13" s="69"/>
+      <c r="P13" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q13" s="70"/>
+      <c r="R13" s="69"/>
+      <c r="S13" s="69"/>
+      <c r="T13" s="69"/>
+    </row>
+    <row r="14" spans="1:20" ht="45.75">
+      <c r="A14" s="72"/>
+      <c r="B14" s="88"/>
+      <c r="C14" s="89"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="90" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="91">
+        <v>0</v>
+      </c>
+      <c r="H14" s="91">
+        <v>170</v>
+      </c>
+      <c r="I14" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="K14" s="69"/>
+      <c r="L14" s="92" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="95"/>
+      <c r="N14" s="69"/>
+      <c r="O14" s="69"/>
+      <c r="P14" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q14" s="70"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="69"/>
+      <c r="T14" s="69"/>
+    </row>
+    <row r="15" spans="1:20" ht="76.5">
+      <c r="A15" s="72"/>
+      <c r="B15" s="88"/>
+      <c r="C15" s="89"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="91"/>
+      <c r="H15" s="91">
+        <v>31</v>
+      </c>
+      <c r="I15" s="96" t="s">
+        <v>77</v>
+      </c>
+      <c r="J15" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="K15" s="97">
+        <v>0.33</v>
+      </c>
+      <c r="L15" s="92" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="95"/>
+      <c r="N15" s="69"/>
+      <c r="O15" s="69"/>
+      <c r="P15" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q15" s="70"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="69"/>
+      <c r="T15" s="69"/>
+    </row>
+    <row r="16" spans="1:20" ht="81">
+      <c r="A16" s="72"/>
+      <c r="B16" s="88"/>
+      <c r="C16" s="89"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="102" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="65"/>
-      <c r="L3" s="49" t="s">
+      <c r="F16" s="103" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" s="104">
+        <v>0</v>
+      </c>
+      <c r="H16" s="104">
+        <v>50</v>
+      </c>
+      <c r="I16" s="105" t="s">
+        <v>79</v>
+      </c>
+      <c r="J16" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="66" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="17"/>
-    </row>
-    <row r="4" spans="1:19" ht="106.5">
-      <c r="A4" s="53"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="8">
+      <c r="K16" s="69"/>
+      <c r="L16" s="92" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" s="95"/>
+      <c r="N16" s="69"/>
+      <c r="O16" s="69"/>
+      <c r="P16" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q16" s="70"/>
+      <c r="R16" s="69"/>
+      <c r="S16" s="69"/>
+      <c r="T16" s="69"/>
+    </row>
+    <row r="17" spans="1:20" ht="76.5">
+      <c r="A17" s="72"/>
+      <c r="B17" s="88"/>
+      <c r="C17" s="89"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="90" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="63" t="s">
+        <v>80</v>
+      </c>
+      <c r="G17" s="91">
         <v>0</v>
       </c>
-      <c r="H4" s="8">
-        <v>1</v>
-      </c>
-      <c r="I4" s="62" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="65"/>
-      <c r="L4" s="49" t="s">
+      <c r="H17" s="91">
+        <v>14</v>
+      </c>
+      <c r="I17" s="96" t="s">
+        <v>81</v>
+      </c>
+      <c r="J17" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="M4" s="67"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-    </row>
-    <row r="5" spans="1:19" ht="60.75">
-      <c r="A5" s="53"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="46" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="8">
-        <v>21000</v>
-      </c>
-      <c r="I5" s="62" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="65"/>
-      <c r="L5" s="49" t="s">
+      <c r="K17" s="69"/>
+      <c r="L17" s="92" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="95"/>
+      <c r="N17" s="69"/>
+      <c r="O17" s="69"/>
+      <c r="P17" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q17" s="70" t="s">
+        <v>60</v>
+      </c>
+      <c r="R17" s="69"/>
+      <c r="S17" s="69"/>
+      <c r="T17" s="69"/>
+    </row>
+    <row r="18" spans="1:20" ht="106.5">
+      <c r="A18" s="68"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="99"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="90" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="63" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="91">
+        <v>108</v>
+      </c>
+      <c r="H18" s="91">
+        <v>348</v>
+      </c>
+      <c r="I18" s="100" t="s">
+        <v>83</v>
+      </c>
+      <c r="J18" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="67"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="17"/>
-    </row>
-    <row r="6" spans="1:19" ht="148.5" customHeight="1">
-      <c r="A6" s="52">
-        <v>5681</v>
-      </c>
-      <c r="B6" s="52" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="50">
-        <v>28210000</v>
-      </c>
-      <c r="E6" s="61" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="6">
-        <v>252178</v>
-      </c>
-      <c r="H6" s="6">
-        <v>441315</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" s="17"/>
-      <c r="L6" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" s="37"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-    </row>
-    <row r="7" spans="1:19" ht="151.5" customHeight="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6">
-        <v>196000</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="K7" s="17"/>
-      <c r="L7" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" s="37"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="17"/>
-      <c r="S7" s="17"/>
-    </row>
-    <row r="8" spans="1:19" ht="105" customHeight="1">
-      <c r="A8" s="53"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="61" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="K8" s="17"/>
-      <c r="L8" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="37"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17"/>
-      <c r="S8" s="17"/>
-    </row>
-    <row r="9" spans="1:19" ht="147.75" customHeight="1">
-      <c r="A9" s="53"/>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="E9" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="5">
-        <v>18</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="K9" s="17"/>
-      <c r="L9" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" s="37"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="17"/>
-      <c r="S9" s="17"/>
-    </row>
-    <row r="10" spans="1:19" ht="86.25" customHeight="1">
-      <c r="A10" s="53"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="J10" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="K10" s="17"/>
-      <c r="L10" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="M10" s="38"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="17"/>
-    </row>
-    <row r="11" spans="1:19" ht="262.5" customHeight="1">
-      <c r="A11" s="54"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="61" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" s="5">
-        <v>5</v>
-      </c>
-      <c r="H11" s="5">
-        <v>11</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="K11" s="17"/>
-      <c r="L11" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="M11" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
-    </row>
-    <row r="12" spans="1:19" ht="106.5">
-      <c r="A12" s="51">
-        <v>5509</v>
-      </c>
-      <c r="B12" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="58" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="51">
-        <v>4532164</v>
-      </c>
-      <c r="E12" s="60" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12" s="19">
-        <v>4</v>
-      </c>
-      <c r="H12" s="19">
-        <v>40</v>
-      </c>
-      <c r="I12" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="J12" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="K12" s="17"/>
-      <c r="L12" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" s="40" t="s">
-        <v>64</v>
-      </c>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-    </row>
-    <row r="13" spans="1:19" ht="30.75">
-      <c r="A13" s="51"/>
-      <c r="B13" s="56"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="60" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13" s="19">
-        <v>0</v>
-      </c>
-      <c r="H13" s="19">
-        <v>435</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="J13" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" s="17"/>
-      <c r="L13" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
-    </row>
-    <row r="14" spans="1:19" ht="45.75">
-      <c r="A14" s="51"/>
-      <c r="B14" s="56"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="60" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14" s="19">
-        <v>0</v>
-      </c>
-      <c r="H14" s="19">
-        <v>170</v>
-      </c>
-      <c r="I14" s="11" t="s">
+      <c r="K18" s="101"/>
+      <c r="L18" s="92" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" s="95"/>
+      <c r="N18" s="69"/>
+      <c r="O18" s="69"/>
+      <c r="P18" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="K14" s="17"/>
-      <c r="L14" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" s="35"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="17"/>
-    </row>
-    <row r="15" spans="1:19" ht="76.5">
-      <c r="A15" s="51"/>
-      <c r="B15" s="56"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="60" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34">
-        <v>31</v>
-      </c>
-      <c r="I15" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="J15" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="K15" s="33">
-        <v>0.33</v>
-      </c>
-      <c r="L15" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" s="35"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="17"/>
-    </row>
-    <row r="16" spans="1:19" ht="81">
-      <c r="A16" s="51"/>
-      <c r="B16" s="56"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="60" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" s="19">
-        <v>0</v>
-      </c>
-      <c r="H16" s="19">
-        <v>50</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="J16" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="K16" s="17"/>
-      <c r="L16" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" s="35"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="17"/>
-    </row>
-    <row r="17" spans="1:19" ht="76.5">
-      <c r="A17" s="51"/>
-      <c r="B17" s="56"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="60" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="G17" s="19">
-        <v>0</v>
-      </c>
-      <c r="H17" s="19">
-        <v>14</v>
-      </c>
-      <c r="I17" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="J17" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="K17" s="17"/>
-      <c r="L17" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="M17" s="35"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="17"/>
-    </row>
-    <row r="18" spans="1:19" ht="106.5">
-      <c r="A18" s="49"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="59"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="60" t="s">
-        <v>61</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18" s="19">
-        <v>108</v>
-      </c>
-      <c r="H18" s="19">
-        <v>348</v>
-      </c>
-      <c r="I18" s="68" t="s">
-        <v>78</v>
-      </c>
-      <c r="J18" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="K18" s="64"/>
-      <c r="L18" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="M18" s="35"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="17"/>
+      <c r="Q18" s="70"/>
+      <c r="R18" s="69"/>
+      <c r="S18" s="69"/>
+      <c r="T18" s="69"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5 E7" xr:uid="{ACE05F1D-CAE5-4EDA-A504-3E8FC4C61FB0}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q18" xr:uid="{ADB713D9-2155-4F34-9D1D-CD9E6A7B2541}">
+      <formula1>"Tier 1, Tier 2, Tier 3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P18" xr:uid="{B9FBFA70-C3E6-461A-ACE3-5CBB2B58B4F9}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
+    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{3D966F76-EC1C-41C6-B94A-6CA9ED00DEB0}"/>
@@ -2056,34 +2212,34 @@
         <v>15</v>
       </c>
       <c r="Q1" s="42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R1" s="42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S1" s="42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T1" s="42"/>
     </row>
     <row r="2" spans="1:20" ht="60.75">
-      <c r="A2" s="69">
+      <c r="A2" s="43">
         <v>6486</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="25">
         <v>5600607</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="8">
         <v>0</v>
@@ -2092,14 +2248,14 @@
         <v>0.75</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="70" t="s">
         <v>24</v>
       </c>
+      <c r="J2" s="44" t="s">
+        <v>25</v>
+      </c>
       <c r="K2" s="17"/>
-      <c r="L2" s="71" t="s">
-        <v>25</v>
+      <c r="L2" s="45" t="s">
+        <v>26</v>
       </c>
       <c r="M2" s="35"/>
       <c r="N2" s="17"/>
@@ -2111,15 +2267,15 @@
       <c r="T2" s="17"/>
     </row>
     <row r="3" spans="1:20" ht="152.25">
-      <c r="A3" s="69"/>
+      <c r="A3" s="43"/>
       <c r="B3" s="25"/>
       <c r="C3" s="25"/>
       <c r="D3" s="25"/>
       <c r="E3" s="22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G3" s="24">
         <v>0</v>
@@ -2128,13 +2284,13 @@
         <v>700000</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="70"/>
+        <v>30</v>
+      </c>
+      <c r="J3" s="44"/>
       <c r="K3" s="17"/>
-      <c r="L3" s="71"/>
+      <c r="L3" s="45"/>
       <c r="M3" s="36" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N3" s="17"/>
       <c r="O3" s="17"/>
@@ -2145,15 +2301,15 @@
       <c r="T3" s="17"/>
     </row>
     <row r="4" spans="1:20" ht="106.5">
-      <c r="A4" s="69"/>
+      <c r="A4" s="43"/>
       <c r="B4" s="25"/>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
       <c r="E4" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4" s="8">
         <v>0</v>
@@ -2162,11 +2318,11 @@
         <v>1</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="70"/>
+        <v>34</v>
+      </c>
+      <c r="J4" s="44"/>
       <c r="K4" s="17"/>
-      <c r="L4" s="71"/>
+      <c r="L4" s="45"/>
       <c r="M4" s="37"/>
       <c r="N4" s="17"/>
       <c r="O4" s="17"/>
@@ -2177,28 +2333,28 @@
       <c r="T4" s="17"/>
     </row>
     <row r="5" spans="1:20" ht="60.75">
-      <c r="A5" s="69"/>
+      <c r="A5" s="43"/>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="E5" s="9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H5" s="8">
         <v>21000</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="70"/>
+        <v>39</v>
+      </c>
+      <c r="J5" s="44"/>
       <c r="K5" s="17"/>
-      <c r="L5" s="71"/>
+      <c r="L5" s="45"/>
       <c r="M5" s="37"/>
       <c r="N5" s="17"/>
       <c r="O5" s="17"/>
@@ -2213,19 +2369,19 @@
         <v>5681</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D6" s="25">
         <v>28210000</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G6" s="6">
         <v>252178</v>
@@ -2234,14 +2390,14 @@
         <v>441315</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="72" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="J6" s="46" t="s">
+        <v>45</v>
       </c>
       <c r="K6" s="17"/>
-      <c r="L6" s="69" t="s">
-        <v>25</v>
+      <c r="L6" s="43" t="s">
+        <v>26</v>
       </c>
       <c r="M6" s="37"/>
       <c r="N6" s="17"/>
@@ -2258,10 +2414,10 @@
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="E7" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G7" s="5">
         <v>0</v>
@@ -2270,11 +2426,11 @@
         <v>196000</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" s="73"/>
+        <v>48</v>
+      </c>
+      <c r="J7" s="47"/>
       <c r="K7" s="17"/>
-      <c r="L7" s="69"/>
+      <c r="L7" s="43"/>
       <c r="M7" s="37"/>
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
@@ -2290,23 +2446,23 @@
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="E8" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="73"/>
+        <v>52</v>
+      </c>
+      <c r="J8" s="47"/>
       <c r="K8" s="17"/>
-      <c r="L8" s="69"/>
+      <c r="L8" s="43"/>
       <c r="M8" s="37"/>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
@@ -2323,20 +2479,20 @@
       <c r="D9" s="25"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H9" s="5">
         <v>18</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="73"/>
+        <v>56</v>
+      </c>
+      <c r="J9" s="47"/>
       <c r="K9" s="17"/>
-      <c r="L9" s="69"/>
+      <c r="L9" s="43"/>
       <c r="M9" s="37"/>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
@@ -2352,21 +2508,21 @@
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="E10" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="J10" s="73"/>
+        <v>59</v>
+      </c>
+      <c r="J10" s="47"/>
       <c r="K10" s="17"/>
-      <c r="L10" s="69"/>
+      <c r="L10" s="43"/>
       <c r="M10" s="38"/>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
@@ -2382,10 +2538,10 @@
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="E11" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G11" s="5">
         <v>5</v>
@@ -2394,13 +2550,13 @@
         <v>11</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" s="74"/>
+        <v>62</v>
+      </c>
+      <c r="J11" s="48"/>
       <c r="K11" s="17"/>
-      <c r="L11" s="69"/>
+      <c r="L11" s="43"/>
       <c r="M11" s="39" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
@@ -2415,19 +2571,19 @@
         <v>5509</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D12" s="25">
         <v>4532164</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G12" s="19">
         <v>4</v>
@@ -2436,15 +2592,15 @@
         <v>40</v>
       </c>
       <c r="I12" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="J12" s="72" t="s">
-        <v>24</v>
+        <v>67</v>
+      </c>
+      <c r="J12" s="46" t="s">
+        <v>25</v>
       </c>
       <c r="K12" s="17"/>
-      <c r="L12" s="69"/>
+      <c r="L12" s="43"/>
       <c r="M12" s="40" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="N12" s="17"/>
       <c r="O12" s="17"/>
@@ -2460,10 +2616,10 @@
       <c r="C13" s="31"/>
       <c r="D13" s="25"/>
       <c r="E13" s="18" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G13" s="19">
         <v>0</v>
@@ -2472,13 +2628,13 @@
         <v>435</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="J13" s="73"/>
+        <v>72</v>
+      </c>
+      <c r="J13" s="47"/>
       <c r="K13" s="17"/>
-      <c r="L13" s="69"/>
+      <c r="L13" s="43"/>
       <c r="M13" s="41" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="N13" s="17"/>
       <c r="O13" s="17"/>
@@ -2494,10 +2650,10 @@
       <c r="C14" s="31"/>
       <c r="D14" s="25"/>
       <c r="E14" s="18" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G14" s="19">
         <v>0</v>
@@ -2506,11 +2662,11 @@
         <v>170</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="J14" s="73"/>
+        <v>74</v>
+      </c>
+      <c r="J14" s="47"/>
       <c r="K14" s="17"/>
-      <c r="L14" s="69"/>
+      <c r="L14" s="43"/>
       <c r="M14" s="35"/>
       <c r="N14" s="17"/>
       <c r="O14" s="17"/>
@@ -2526,23 +2682,23 @@
       <c r="C15" s="31"/>
       <c r="D15" s="25"/>
       <c r="E15" s="18" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G15" s="34">
         <v>31</v>
       </c>
       <c r="H15" s="34"/>
       <c r="I15" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="J15" s="73"/>
+        <v>77</v>
+      </c>
+      <c r="J15" s="47"/>
       <c r="K15" s="33">
         <v>0.33</v>
       </c>
-      <c r="L15" s="69"/>
+      <c r="L15" s="43"/>
       <c r="M15" s="35"/>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
@@ -2558,10 +2714,10 @@
       <c r="C16" s="31"/>
       <c r="D16" s="25"/>
       <c r="E16" s="18" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -2570,11 +2726,11 @@
         <v>50</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="J16" s="73"/>
+        <v>79</v>
+      </c>
+      <c r="J16" s="47"/>
       <c r="K16" s="17"/>
-      <c r="L16" s="69"/>
+      <c r="L16" s="43"/>
       <c r="M16" s="35"/>
       <c r="N16" s="17"/>
       <c r="O16" s="17"/>
@@ -2590,10 +2746,10 @@
       <c r="C17" s="31"/>
       <c r="D17" s="25"/>
       <c r="E17" s="18" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -2602,11 +2758,11 @@
         <v>14</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="J17" s="73"/>
+        <v>81</v>
+      </c>
+      <c r="J17" s="47"/>
       <c r="K17" s="17"/>
-      <c r="L17" s="69"/>
+      <c r="L17" s="43"/>
       <c r="M17" s="35"/>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
@@ -2622,10 +2778,10 @@
       <c r="C18" s="32"/>
       <c r="D18" s="25"/>
       <c r="E18" s="18" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G18" s="19">
         <v>108</v>
@@ -2634,11 +2790,11 @@
         <v>348</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="J18" s="74"/>
+        <v>83</v>
+      </c>
+      <c r="J18" s="48"/>
       <c r="K18" s="17"/>
-      <c r="L18" s="69"/>
+      <c r="L18" s="43"/>
       <c r="M18" s="35"/>
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
@@ -2745,34 +2901,34 @@
         <v>15</v>
       </c>
       <c r="Q1" s="42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R1" s="42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S1" s="42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T1" s="42"/>
     </row>
     <row r="2" spans="1:20" ht="60.75">
-      <c r="A2" s="69">
+      <c r="A2" s="43">
         <v>6486</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="25">
         <v>5600607</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="8">
         <v>0</v>
@@ -2781,14 +2937,14 @@
         <v>0.75</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="70" t="s">
         <v>24</v>
       </c>
+      <c r="J2" s="44" t="s">
+        <v>25</v>
+      </c>
       <c r="K2" s="17"/>
-      <c r="L2" s="71" t="s">
-        <v>25</v>
+      <c r="L2" s="45" t="s">
+        <v>26</v>
       </c>
       <c r="M2" s="35"/>
       <c r="N2" s="17"/>
@@ -2800,15 +2956,15 @@
       <c r="T2" s="17"/>
     </row>
     <row r="3" spans="1:20" ht="152.25">
-      <c r="A3" s="69"/>
+      <c r="A3" s="43"/>
       <c r="B3" s="25"/>
       <c r="C3" s="25"/>
       <c r="D3" s="25"/>
       <c r="E3" s="22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G3" s="24">
         <v>0</v>
@@ -2817,13 +2973,13 @@
         <v>700000</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="70"/>
+        <v>30</v>
+      </c>
+      <c r="J3" s="44"/>
       <c r="K3" s="17"/>
-      <c r="L3" s="71"/>
+      <c r="L3" s="45"/>
       <c r="M3" s="36" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N3" s="17"/>
       <c r="O3" s="17"/>
@@ -2834,15 +2990,15 @@
       <c r="T3" s="17"/>
     </row>
     <row r="4" spans="1:20" ht="106.5">
-      <c r="A4" s="69"/>
+      <c r="A4" s="43"/>
       <c r="B4" s="25"/>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
       <c r="E4" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4" s="8">
         <v>0</v>
@@ -2851,11 +3007,11 @@
         <v>1</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="70"/>
+        <v>34</v>
+      </c>
+      <c r="J4" s="44"/>
       <c r="K4" s="17"/>
-      <c r="L4" s="71"/>
+      <c r="L4" s="45"/>
       <c r="M4" s="37"/>
       <c r="N4" s="17"/>
       <c r="O4" s="17"/>
@@ -2866,28 +3022,28 @@
       <c r="T4" s="17"/>
     </row>
     <row r="5" spans="1:20" ht="60.75">
-      <c r="A5" s="69"/>
+      <c r="A5" s="43"/>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="E5" s="9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H5" s="8">
         <v>21000</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="70"/>
+        <v>39</v>
+      </c>
+      <c r="J5" s="44"/>
       <c r="K5" s="17"/>
-      <c r="L5" s="71"/>
+      <c r="L5" s="45"/>
       <c r="M5" s="37"/>
       <c r="N5" s="17"/>
       <c r="O5" s="17"/>
@@ -2902,19 +3058,19 @@
         <v>5681</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D6" s="25">
         <v>28210000</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G6" s="6">
         <v>252178</v>
@@ -2923,14 +3079,14 @@
         <v>441315</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="72" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="J6" s="46" t="s">
+        <v>45</v>
       </c>
       <c r="K6" s="17"/>
-      <c r="L6" s="69" t="s">
-        <v>25</v>
+      <c r="L6" s="43" t="s">
+        <v>26</v>
       </c>
       <c r="M6" s="37"/>
       <c r="N6" s="17"/>
@@ -2947,10 +3103,10 @@
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="E7" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G7" s="5">
         <v>0</v>
@@ -2959,11 +3115,11 @@
         <v>196000</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" s="73"/>
+        <v>48</v>
+      </c>
+      <c r="J7" s="47"/>
       <c r="K7" s="17"/>
-      <c r="L7" s="69"/>
+      <c r="L7" s="43"/>
       <c r="M7" s="37"/>
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
@@ -2979,23 +3135,23 @@
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="E8" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="73"/>
+        <v>52</v>
+      </c>
+      <c r="J8" s="47"/>
       <c r="K8" s="17"/>
-      <c r="L8" s="69"/>
+      <c r="L8" s="43"/>
       <c r="M8" s="37"/>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
@@ -3012,20 +3168,20 @@
       <c r="D9" s="25"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H9" s="5">
         <v>18</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="73"/>
+        <v>56</v>
+      </c>
+      <c r="J9" s="47"/>
       <c r="K9" s="17"/>
-      <c r="L9" s="69"/>
+      <c r="L9" s="43"/>
       <c r="M9" s="37"/>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
@@ -3041,21 +3197,21 @@
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="E10" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="J10" s="73"/>
+        <v>59</v>
+      </c>
+      <c r="J10" s="47"/>
       <c r="K10" s="17"/>
-      <c r="L10" s="69"/>
+      <c r="L10" s="43"/>
       <c r="M10" s="38"/>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
@@ -3071,10 +3227,10 @@
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="E11" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G11" s="5">
         <v>5</v>
@@ -3083,13 +3239,13 @@
         <v>11</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" s="74"/>
+        <v>62</v>
+      </c>
+      <c r="J11" s="48"/>
       <c r="K11" s="17"/>
-      <c r="L11" s="69"/>
+      <c r="L11" s="43"/>
       <c r="M11" s="39" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
@@ -3104,19 +3260,19 @@
         <v>5509</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D12" s="25">
         <v>4532164</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G12" s="19">
         <v>4</v>
@@ -3125,15 +3281,15 @@
         <v>40</v>
       </c>
       <c r="I12" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="J12" s="72" t="s">
-        <v>24</v>
+        <v>67</v>
+      </c>
+      <c r="J12" s="46" t="s">
+        <v>25</v>
       </c>
       <c r="K12" s="17"/>
-      <c r="L12" s="69"/>
+      <c r="L12" s="43"/>
       <c r="M12" s="40" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="N12" s="17"/>
       <c r="O12" s="17"/>
@@ -3149,10 +3305,10 @@
       <c r="C13" s="31"/>
       <c r="D13" s="25"/>
       <c r="E13" s="18" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G13" s="19">
         <v>0</v>
@@ -3161,13 +3317,13 @@
         <v>435</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="J13" s="73"/>
+        <v>72</v>
+      </c>
+      <c r="J13" s="47"/>
       <c r="K13" s="17"/>
-      <c r="L13" s="69"/>
+      <c r="L13" s="43"/>
       <c r="M13" s="41" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="N13" s="17"/>
       <c r="O13" s="17"/>
@@ -3183,10 +3339,10 @@
       <c r="C14" s="31"/>
       <c r="D14" s="25"/>
       <c r="E14" s="18" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G14" s="19">
         <v>0</v>
@@ -3195,11 +3351,11 @@
         <v>170</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="J14" s="73"/>
+        <v>74</v>
+      </c>
+      <c r="J14" s="47"/>
       <c r="K14" s="17"/>
-      <c r="L14" s="69"/>
+      <c r="L14" s="43"/>
       <c r="M14" s="35"/>
       <c r="N14" s="17"/>
       <c r="O14" s="17"/>
@@ -3215,23 +3371,23 @@
       <c r="C15" s="31"/>
       <c r="D15" s="25"/>
       <c r="E15" s="18" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G15" s="34">
         <v>31</v>
       </c>
       <c r="H15" s="34"/>
       <c r="I15" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="J15" s="73"/>
+        <v>77</v>
+      </c>
+      <c r="J15" s="47"/>
       <c r="K15" s="33">
         <v>0.33</v>
       </c>
-      <c r="L15" s="69"/>
+      <c r="L15" s="43"/>
       <c r="M15" s="35"/>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
@@ -3247,10 +3403,10 @@
       <c r="C16" s="31"/>
       <c r="D16" s="25"/>
       <c r="E16" s="18" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -3259,11 +3415,11 @@
         <v>50</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="J16" s="73"/>
+        <v>79</v>
+      </c>
+      <c r="J16" s="47"/>
       <c r="K16" s="17"/>
-      <c r="L16" s="69"/>
+      <c r="L16" s="43"/>
       <c r="M16" s="35"/>
       <c r="N16" s="17"/>
       <c r="O16" s="17"/>
@@ -3279,10 +3435,10 @@
       <c r="C17" s="31"/>
       <c r="D17" s="25"/>
       <c r="E17" s="18" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -3291,11 +3447,11 @@
         <v>14</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="J17" s="73"/>
+        <v>81</v>
+      </c>
+      <c r="J17" s="47"/>
       <c r="K17" s="17"/>
-      <c r="L17" s="69"/>
+      <c r="L17" s="43"/>
       <c r="M17" s="35"/>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
@@ -3311,10 +3467,10 @@
       <c r="C18" s="32"/>
       <c r="D18" s="25"/>
       <c r="E18" s="18" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G18" s="19">
         <v>108</v>
@@ -3323,11 +3479,11 @@
         <v>348</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="J18" s="74"/>
+        <v>83</v>
+      </c>
+      <c r="J18" s="48"/>
       <c r="K18" s="17"/>
-      <c r="L18" s="69"/>
+      <c r="L18" s="43"/>
       <c r="M18" s="35"/>
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
@@ -3380,160 +3536,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="75" t="s">
-        <v>81</v>
+      <c r="A2" s="49" t="s">
+        <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="75"/>
+      <c r="A3" s="49"/>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="75"/>
+      <c r="A4" s="49"/>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="76" t="s">
-        <v>86</v>
+      <c r="A5" s="50" t="s">
+        <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="76"/>
+      <c r="A6" s="50"/>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="76"/>
+      <c r="A7" s="50"/>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="76"/>
+      <c r="A8" s="50"/>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="76"/>
+      <c r="A9" s="50"/>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="77" t="s">
-        <v>97</v>
+      <c r="A10" s="51" t="s">
+        <v>102</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="77"/>
+      <c r="A11" s="51"/>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="78" t="s">
-        <v>100</v>
+      <c r="A12" s="52" t="s">
+        <v>105</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="78"/>
+      <c r="A13" s="52"/>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="78"/>
+      <c r="A14" s="52"/>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B16" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -3548,6 +3704,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -3796,28 +3972,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A2994FF-555A-4817-9517-48283D9AFFB0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34ACB9F2-A8B7-4727-8BFC-2C58CAD1DCBF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3825,5 +3981,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34ACB9F2-A8B7-4727-8BFC-2C58CAD1DCBF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A2994FF-555A-4817-9517-48283D9AFFB0}"/>
 </file>
--- a/01_Input/00_CO Validation/Mauritius - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Mauritius - Energy Projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28521"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="432" documentId="11_22A4E67450481778D11D2BA3F348756C7829339C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D190315-F0FA-454D-959E-E77480DF73B2}"/>
+  <xr:revisionPtr revIDLastSave="444" documentId="11_22A4E67450481778D11D2BA3F348756C7829339C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B7C931E-131F-42E8-9F44-9FEEE00D16B7}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="131">
   <si>
     <t>Project ID</t>
   </si>
@@ -48,6 +48,9 @@
     <t>Budget</t>
   </si>
   <si>
+    <t>Country</t>
+  </si>
+  <si>
     <t>Beneficiary Category</t>
   </si>
   <si>
@@ -108,7 +111,10 @@
     <t>Promoting Low-carbon Electric Public Bus Transport in Mauritius</t>
   </si>
   <si>
-    <t>6486 Promoting Low-carbon Electric Public Bus Transport in Mauritius (undp.org)</t>
+    <t>https://co.pims.undp.org/project/view?id=6486</t>
+  </si>
+  <si>
+    <t>Mauritius</t>
   </si>
   <si>
     <t>Energy (MW added)</t>
@@ -195,7 +201,7 @@
     <t>Transformational shift to a low-carbon economy</t>
   </si>
   <si>
-    <t>5681 Transformational shift to a low-carbon economy (undp.org)</t>
+    <t>https://co.pims.undp.org/project/view?id=5681</t>
   </si>
   <si>
     <t>Electricity Access</t>
@@ -288,6 +294,9 @@
   </si>
   <si>
     <t xml:space="preserve">Realising Energy Savings and Climate Benefits of Implementing Mandatory Energy Auditing in the Republic of Mauritius </t>
+  </si>
+  <si>
+    <t>https://co.pims.undp.org/project/view?id=5509</t>
   </si>
   <si>
     <t>Medium Enterprises</t>
@@ -372,7 +381,13 @@
     <t>Baseline : Before the project: 108 firms as of March 2018   End of Project:  80 firms beyond baseline from among the 650 largest energy consumers, plus 160 SMEs (Additional of 240 over the baseline of 108 equals 348).</t>
   </si>
   <si>
+    <t>6486 Promoting Low-carbon Electric Public Bus Transport in Mauritius (undp.org)</t>
+  </si>
+  <si>
     <t>Transport Services</t>
+  </si>
+  <si>
+    <t>5681 Transformational shift to a low-carbon economy (undp.org)</t>
   </si>
   <si>
     <t>Capacity Training</t>
@@ -621,7 +636,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -769,12 +784,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -893,9 +920,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -993,6 +1017,39 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1011,33 +1068,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="3">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1340,28 +1383,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1EA8529-86F5-4E00-BF5D-B1BB315D4BA2}">
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="66.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="35.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="50.85546875" customWidth="1"/>
-    <col min="13" max="13" width="56.5703125" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.42578125" customWidth="1"/>
-    <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="50.85546875" customWidth="1"/>
+    <col min="14" max="14" width="56.5703125" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" customWidth="1"/>
+    <col min="19" max="19" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
@@ -1374,7 +1417,7 @@
       <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="41" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="11" t="s">
@@ -1386,827 +1429,852 @@
       <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="L1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="39" t="s">
+      <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="42" t="s">
+      <c r="O1" s="39" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="92" t="s">
+      <c r="Q1" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="92" t="s">
+      <c r="R1" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="93" t="s">
+      <c r="S1" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="39" t="s">
+      <c r="T1" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="93" t="s">
+      <c r="U1" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="93" t="s">
+      <c r="V1" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="39" t="s">
+      <c r="W1" s="83" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" ht="60.75">
+      <c r="X1" s="39" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="60.75">
       <c r="A2" s="43">
         <v>6486</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="45">
+      <c r="C2" s="88" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="44">
         <v>5600607</v>
       </c>
-      <c r="E2" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="47" t="s">
+      <c r="E2" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="48">
+      <c r="F2" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="47">
         <v>0</v>
       </c>
-      <c r="H2" s="48">
+      <c r="I2" s="47">
         <v>0.75</v>
       </c>
-      <c r="I2" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="51"/>
-      <c r="L2" s="52" t="s">
+      <c r="J2" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="51"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="61" t="s">
+      <c r="K2" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="40"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="50"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="60" t="s">
+        <v>32</v>
+      </c>
       <c r="Q2" s="40"/>
       <c r="R2" s="40"/>
       <c r="S2" s="40"/>
-      <c r="T2" s="22" t="s">
+      <c r="T2" s="40"/>
+      <c r="U2" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="V2" s="40"/>
+      <c r="W2" s="40"/>
+      <c r="X2" s="22"/>
+    </row>
+    <row r="3" spans="1:24" ht="152.25">
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="47">
+        <v>0</v>
+      </c>
+      <c r="I3" s="47">
+        <v>700000</v>
+      </c>
+      <c r="J3" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="50"/>
+      <c r="M3" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="22"/>
-    </row>
-    <row r="3" spans="1:23" ht="152.25">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="46" t="s">
+      <c r="N3" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="14"/>
+      <c r="P3" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="55" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="48">
-        <v>0</v>
-      </c>
-      <c r="H3" s="48">
-        <v>700000</v>
-      </c>
-      <c r="I3" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="51"/>
-      <c r="L3" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" s="56" t="s">
-        <v>35</v>
-      </c>
-      <c r="N3" s="14"/>
-      <c r="O3" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="P3" s="40"/>
       <c r="Q3" s="40"/>
       <c r="R3" s="40"/>
       <c r="S3" s="40"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="22"/>
       <c r="V3" s="40"/>
-      <c r="W3" s="22"/>
-    </row>
-    <row r="4" spans="1:23" ht="106.5">
-      <c r="A4" s="53"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="48">
+      <c r="W3" s="40"/>
+      <c r="X3" s="22"/>
+    </row>
+    <row r="4" spans="1:24" ht="106.5">
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="47">
         <v>0</v>
       </c>
-      <c r="H4" s="48">
+      <c r="I4" s="47">
         <v>1</v>
       </c>
-      <c r="I4" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="51"/>
-      <c r="L4" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="58"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="61" t="s">
+      <c r="J4" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="P4" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="40" t="s">
-        <v>39</v>
-      </c>
+      <c r="L4" s="50"/>
+      <c r="M4" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" s="57"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="40"/>
       <c r="S4" s="40" t="s">
-        <v>40</v>
-      </c>
-      <c r="T4" s="22"/>
-      <c r="U4" s="40"/>
-      <c r="V4" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="W4" s="22"/>
-    </row>
-    <row r="5" spans="1:23" ht="60.75">
-      <c r="A5" s="53"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="79" t="s">
+      <c r="T4" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="59" t="s">
+      <c r="U4" s="22"/>
+      <c r="V4" s="40"/>
+      <c r="W4" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="48" t="s">
+      <c r="X4" s="22"/>
+    </row>
+    <row r="5" spans="1:24" ht="60.75">
+      <c r="A5" s="52"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="86"/>
+      <c r="F5" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="48">
+      <c r="G5" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="47">
         <v>21000</v>
       </c>
-      <c r="I5" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="51"/>
-      <c r="L5" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="58"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="61" t="s">
+      <c r="J5" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="P5" s="40"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="57"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="60" t="s">
+        <v>32</v>
+      </c>
       <c r="Q5" s="40"/>
       <c r="R5" s="40"/>
       <c r="S5" s="40"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="40"/>
+      <c r="T5" s="40"/>
+      <c r="U5" s="22"/>
       <c r="V5" s="40"/>
-      <c r="W5" s="22"/>
-    </row>
-    <row r="6" spans="1:23" ht="148.5" customHeight="1">
+      <c r="W5" s="40"/>
+      <c r="X5" s="22"/>
+    </row>
+    <row r="6" spans="1:24" ht="148.5" customHeight="1">
       <c r="A6" s="43">
         <v>5681</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="45">
+        <v>48</v>
+      </c>
+      <c r="C6" s="88" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="44">
         <v>28210000</v>
       </c>
-      <c r="E6" s="61" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="62" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="48">
+      <c r="E6" s="84" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="61" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" s="47">
         <v>252178</v>
       </c>
-      <c r="H6" s="48">
+      <c r="I6" s="47">
         <v>441315</v>
       </c>
-      <c r="I6" s="63" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" s="64" t="s">
-        <v>51</v>
-      </c>
-      <c r="K6" s="14"/>
-      <c r="L6" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="34"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="40"/>
+      <c r="J6" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" s="14"/>
+      <c r="M6" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="34"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="60" t="s">
+        <v>32</v>
+      </c>
       <c r="Q6" s="40"/>
       <c r="R6" s="40"/>
       <c r="S6" s="40"/>
-      <c r="T6" s="22" t="s">
+      <c r="T6" s="40"/>
+      <c r="U6" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="V6" s="40"/>
+      <c r="W6" s="40"/>
+      <c r="X6" s="22"/>
+    </row>
+    <row r="7" spans="1:24" ht="151.5" customHeight="1">
+      <c r="A7" s="52"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="60" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="61">
+        <v>0</v>
+      </c>
+      <c r="I7" s="47">
+        <v>196000</v>
+      </c>
+      <c r="J7" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="14"/>
+      <c r="M7" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="U6" s="40"/>
-      <c r="V6" s="40"/>
-      <c r="W6" s="22"/>
-    </row>
-    <row r="7" spans="1:23" ht="151.5" customHeight="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="61" t="s">
-        <v>52</v>
-      </c>
-      <c r="F7" s="62" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" s="62">
-        <v>0</v>
-      </c>
-      <c r="H7" s="48">
-        <v>196000</v>
-      </c>
-      <c r="I7" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="J7" s="64" t="s">
-        <v>51</v>
-      </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7" s="34"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="P7" s="40"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="60" t="s">
+        <v>32</v>
+      </c>
       <c r="Q7" s="40"/>
       <c r="R7" s="40"/>
       <c r="S7" s="40"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="40"/>
+      <c r="T7" s="40"/>
+      <c r="U7" s="22"/>
       <c r="V7" s="40"/>
-      <c r="W7" s="22"/>
-    </row>
-    <row r="8" spans="1:23" ht="105" customHeight="1">
-      <c r="A8" s="53"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="61" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="62" t="s">
+      <c r="W7" s="40"/>
+      <c r="X7" s="22"/>
+    </row>
+    <row r="8" spans="1:24" ht="105" customHeight="1">
+      <c r="A8" s="52"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="63" t="s">
+      <c r="H8" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="J8" s="64" t="s">
-        <v>51</v>
-      </c>
-      <c r="K8" s="14"/>
-      <c r="L8" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="M8" s="34"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="P8" s="40"/>
+      <c r="I8" s="61" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="K8" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="14"/>
+      <c r="M8" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8" s="34"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="60" t="s">
+        <v>32</v>
+      </c>
       <c r="Q8" s="40"/>
       <c r="R8" s="40"/>
       <c r="S8" s="40"/>
-      <c r="T8" s="22" t="s">
+      <c r="T8" s="40"/>
+      <c r="U8" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="V8" s="40"/>
+      <c r="W8" s="40"/>
+      <c r="X8" s="22"/>
+    </row>
+    <row r="9" spans="1:24" ht="147.75" customHeight="1">
+      <c r="A9" s="52"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="F9" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="61" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="61" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" s="61">
+        <v>18</v>
+      </c>
+      <c r="J9" s="62" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="14"/>
+      <c r="M9" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="U8" s="40"/>
-      <c r="V8" s="40"/>
-      <c r="W8" s="22"/>
-    </row>
-    <row r="9" spans="1:23" ht="147.75" customHeight="1">
-      <c r="A9" s="53"/>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="E9" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="62" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" s="62" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9" s="62">
-        <v>18</v>
-      </c>
-      <c r="I9" s="63" t="s">
-        <v>62</v>
-      </c>
-      <c r="J9" s="64" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="M9" s="34"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="P9" s="40"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="60" t="s">
+        <v>32</v>
+      </c>
       <c r="Q9" s="40"/>
       <c r="R9" s="40"/>
       <c r="S9" s="40"/>
-      <c r="T9" s="22"/>
-      <c r="U9" s="40"/>
+      <c r="T9" s="40"/>
+      <c r="U9" s="22"/>
       <c r="V9" s="40"/>
-      <c r="W9" s="22"/>
-    </row>
-    <row r="10" spans="1:23" ht="86.25" customHeight="1">
-      <c r="A10" s="53"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="61" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="62" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" s="62" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10" s="62"/>
-      <c r="I10" s="63" t="s">
+      <c r="W9" s="40"/>
+      <c r="X9" s="22"/>
+    </row>
+    <row r="10" spans="1:24" ht="86.25" customHeight="1">
+      <c r="A10" s="52"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="64" t="s">
-        <v>51</v>
-      </c>
-      <c r="K10" s="14"/>
-      <c r="L10" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="M10" s="35"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="P10" s="40"/>
+      <c r="H10" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10" s="61"/>
+      <c r="J10" s="62" t="s">
+        <v>67</v>
+      </c>
+      <c r="K10" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="14"/>
+      <c r="M10" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="N10" s="35"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="60" t="s">
+        <v>32</v>
+      </c>
       <c r="Q10" s="40"/>
       <c r="R10" s="40"/>
       <c r="S10" s="40"/>
-      <c r="T10" s="22"/>
-      <c r="U10" s="40"/>
+      <c r="T10" s="40"/>
+      <c r="U10" s="22"/>
       <c r="V10" s="40"/>
-      <c r="W10" s="22"/>
-    </row>
-    <row r="11" spans="1:23" ht="262.5" customHeight="1">
-      <c r="A11" s="65"/>
-      <c r="B11" s="65"/>
-      <c r="C11" s="65"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="62" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11" s="62">
+      <c r="W10" s="40"/>
+      <c r="X10" s="22"/>
+    </row>
+    <row r="11" spans="1:24" ht="262.5" customHeight="1">
+      <c r="A11" s="64"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="61">
         <v>5</v>
       </c>
-      <c r="H11" s="62">
+      <c r="I11" s="61">
         <v>11</v>
       </c>
-      <c r="I11" s="63" t="s">
-        <v>67</v>
-      </c>
-      <c r="J11" s="64" t="s">
-        <v>51</v>
-      </c>
-      <c r="K11" s="14"/>
-      <c r="L11" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="M11" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="N11" s="14"/>
-      <c r="O11" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="P11" s="40"/>
+      <c r="J11" s="62" t="s">
+        <v>69</v>
+      </c>
+      <c r="K11" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11" s="14"/>
+      <c r="M11" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="N11" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="O11" s="14"/>
+      <c r="P11" s="60" t="s">
+        <v>32</v>
+      </c>
       <c r="Q11" s="40"/>
       <c r="R11" s="40"/>
       <c r="S11" s="40"/>
-      <c r="T11" s="22" t="s">
+      <c r="T11" s="40"/>
+      <c r="U11" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="V11" s="40"/>
+      <c r="W11" s="40"/>
+      <c r="X11" s="22"/>
+    </row>
+    <row r="12" spans="1:24" ht="106.5">
+      <c r="A12" s="53">
+        <v>5509</v>
+      </c>
+      <c r="B12" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="89" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="53">
+        <v>4532164</v>
+      </c>
+      <c r="E12" s="84" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="68">
+        <v>4</v>
+      </c>
+      <c r="I12" s="68">
+        <v>40</v>
+      </c>
+      <c r="J12" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="L12" s="14"/>
+      <c r="M12" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="U11" s="40"/>
-      <c r="V11" s="40"/>
-      <c r="W11" s="22"/>
-    </row>
-    <row r="12" spans="1:23" ht="106.5">
-      <c r="A12" s="54">
-        <v>5509</v>
-      </c>
-      <c r="B12" s="66" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="67" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" s="54">
-        <v>4532164</v>
-      </c>
-      <c r="E12" s="68" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="69">
-        <v>4</v>
-      </c>
-      <c r="H12" s="69">
-        <v>40</v>
-      </c>
-      <c r="I12" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="J12" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12" s="14"/>
-      <c r="L12" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M12" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="N12" s="14"/>
-      <c r="O12" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="P12" s="40"/>
+      <c r="N12" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="O12" s="14"/>
+      <c r="P12" s="60" t="s">
+        <v>32</v>
+      </c>
       <c r="Q12" s="40"/>
       <c r="R12" s="40"/>
       <c r="S12" s="40"/>
-      <c r="T12" s="22"/>
-      <c r="U12" s="40"/>
+      <c r="T12" s="40"/>
+      <c r="U12" s="22"/>
       <c r="V12" s="40"/>
-      <c r="W12" s="22"/>
-    </row>
-    <row r="13" spans="1:23" ht="60.75">
-      <c r="A13" s="54"/>
-      <c r="B13" s="66"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="68" t="s">
-        <v>74</v>
-      </c>
-      <c r="F13" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="G13" s="69">
+      <c r="W12" s="40"/>
+      <c r="X12" s="22"/>
+    </row>
+    <row r="13" spans="1:24" ht="45.75">
+      <c r="A13" s="53"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="85"/>
+      <c r="F13" s="67" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" s="68">
         <v>0</v>
       </c>
-      <c r="H13" s="69">
+      <c r="I13" s="68">
         <v>435</v>
       </c>
-      <c r="I13" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="J13" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M13" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="N13" s="14"/>
-      <c r="O13" s="61" t="s">
+      <c r="J13" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="K13" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="P13" s="40"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="O13" s="14"/>
+      <c r="P13" s="60" t="s">
+        <v>32</v>
+      </c>
       <c r="Q13" s="40"/>
       <c r="R13" s="40"/>
       <c r="S13" s="40"/>
-      <c r="T13" s="22"/>
-      <c r="U13" s="40"/>
+      <c r="T13" s="40"/>
+      <c r="U13" s="22"/>
       <c r="V13" s="40"/>
-      <c r="W13" s="22"/>
-    </row>
-    <row r="14" spans="1:23" ht="60.75">
-      <c r="A14" s="54"/>
-      <c r="B14" s="66"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="68" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="69">
+      <c r="W13" s="40"/>
+      <c r="X13" s="22"/>
+    </row>
+    <row r="14" spans="1:24" ht="45.75">
+      <c r="A14" s="53"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="85"/>
+      <c r="F14" s="67" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" s="68">
         <v>0</v>
       </c>
-      <c r="H14" s="69">
+      <c r="I14" s="68">
         <v>170</v>
       </c>
-      <c r="I14" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="J14" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M14" s="32"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="61" t="s">
-        <v>79</v>
-      </c>
-      <c r="P14" s="40"/>
+      <c r="J14" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="K14" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="L14" s="14"/>
+      <c r="M14" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="N14" s="32"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="60" t="s">
+        <v>82</v>
+      </c>
       <c r="Q14" s="40"/>
       <c r="R14" s="40"/>
       <c r="S14" s="40"/>
-      <c r="T14" s="22"/>
-      <c r="U14" s="40"/>
+      <c r="T14" s="40"/>
+      <c r="U14" s="22"/>
       <c r="V14" s="40"/>
-      <c r="W14" s="22"/>
-    </row>
-    <row r="15" spans="1:23" ht="76.5">
-      <c r="A15" s="54"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="86" t="s">
-        <v>80</v>
-      </c>
-      <c r="F15" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="69"/>
-      <c r="H15" s="69">
+      <c r="W14" s="40"/>
+      <c r="X14" s="22"/>
+    </row>
+    <row r="15" spans="1:24" ht="76.5">
+      <c r="A15" s="53"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="79" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="46" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="68"/>
+      <c r="I15" s="68">
         <v>31</v>
       </c>
-      <c r="I15" s="70" t="s">
+      <c r="J15" s="69" t="s">
+        <v>85</v>
+      </c>
+      <c r="K15" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="L15" s="30">
+        <v>0.33</v>
+      </c>
+      <c r="M15" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="N15" s="32"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="60" t="s">
         <v>82</v>
       </c>
-      <c r="J15" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="K15" s="30">
-        <v>0.33</v>
-      </c>
-      <c r="L15" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M15" s="32"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="61" t="s">
-        <v>79</v>
-      </c>
-      <c r="P15" s="40"/>
       <c r="Q15" s="40"/>
       <c r="R15" s="40"/>
       <c r="S15" s="40"/>
-      <c r="T15" s="22"/>
-      <c r="U15" s="40"/>
+      <c r="T15" s="40"/>
+      <c r="U15" s="22"/>
       <c r="V15" s="40"/>
-      <c r="W15" s="22"/>
-    </row>
-    <row r="16" spans="1:23" ht="81">
-      <c r="A16" s="54"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="67"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="75" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="76" t="s">
-        <v>83</v>
-      </c>
-      <c r="G16" s="77">
+      <c r="W15" s="40"/>
+      <c r="X15" s="22"/>
+    </row>
+    <row r="16" spans="1:24" ht="81">
+      <c r="A16" s="53"/>
+      <c r="B16" s="65"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="75" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="76">
         <v>0</v>
       </c>
-      <c r="H16" s="77">
+      <c r="I16" s="76">
         <v>50</v>
       </c>
-      <c r="I16" s="78" t="s">
-        <v>84</v>
-      </c>
-      <c r="J16" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="K16" s="14"/>
-      <c r="L16" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M16" s="32"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="61" t="s">
-        <v>79</v>
-      </c>
-      <c r="P16" s="40"/>
+      <c r="J16" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="K16" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="L16" s="14"/>
+      <c r="M16" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="N16" s="32"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="60" t="s">
+        <v>82</v>
+      </c>
       <c r="Q16" s="40"/>
       <c r="R16" s="40"/>
       <c r="S16" s="40"/>
-      <c r="T16" s="22"/>
-      <c r="U16" s="40"/>
+      <c r="T16" s="40"/>
+      <c r="U16" s="22"/>
       <c r="V16" s="40"/>
-      <c r="W16" s="22"/>
-    </row>
-    <row r="17" spans="1:23" ht="76.5">
-      <c r="A17" s="54"/>
-      <c r="B17" s="66"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="68" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="G17" s="69">
+      <c r="W16" s="40"/>
+      <c r="X16" s="22"/>
+    </row>
+    <row r="17" spans="1:24" ht="76.5">
+      <c r="A17" s="53"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" s="68">
         <v>0</v>
       </c>
-      <c r="H17" s="69">
+      <c r="I17" s="68">
         <v>14</v>
       </c>
-      <c r="I17" s="70" t="s">
-        <v>86</v>
-      </c>
-      <c r="J17" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="K17" s="14"/>
-      <c r="L17" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M17" s="32"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="61" t="s">
-        <v>79</v>
-      </c>
-      <c r="P17" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q17" s="40"/>
-      <c r="R17" s="40" t="s">
-        <v>88</v>
-      </c>
+      <c r="J17" s="69" t="s">
+        <v>89</v>
+      </c>
+      <c r="K17" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="L17" s="14"/>
+      <c r="M17" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" s="32"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="60" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q17" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="R17" s="40"/>
       <c r="S17" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="T17" s="22"/>
-      <c r="U17" s="40"/>
-      <c r="V17" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="W17" s="22"/>
-    </row>
-    <row r="18" spans="1:23" ht="106.5">
-      <c r="A18" s="52"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="68" t="s">
-        <v>70</v>
-      </c>
-      <c r="F18" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="69">
+        <v>91</v>
+      </c>
+      <c r="T17" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="U17" s="22"/>
+      <c r="V17" s="40"/>
+      <c r="W17" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="X17" s="22"/>
+    </row>
+    <row r="18" spans="1:24" ht="106.5">
+      <c r="A18" s="51"/>
+      <c r="B18" s="70"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="68">
         <v>108</v>
       </c>
-      <c r="H18" s="69">
+      <c r="I18" s="68">
         <v>348</v>
       </c>
-      <c r="I18" s="73" t="s">
-        <v>90</v>
-      </c>
-      <c r="J18" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="K18" s="74"/>
-      <c r="L18" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M18" s="32"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="61" t="s">
-        <v>79</v>
-      </c>
-      <c r="P18" s="40"/>
+      <c r="J18" s="72" t="s">
+        <v>93</v>
+      </c>
+      <c r="K18" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="L18" s="73"/>
+      <c r="M18" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="N18" s="32"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="60" t="s">
+        <v>82</v>
+      </c>
       <c r="Q18" s="40"/>
       <c r="R18" s="40"/>
       <c r="S18" s="40"/>
-      <c r="T18" s="22"/>
-      <c r="U18" s="40"/>
+      <c r="T18" s="40"/>
+      <c r="U18" s="22"/>
       <c r="V18" s="40"/>
-      <c r="W18" s="22"/>
+      <c r="W18" s="40"/>
+      <c r="X18" s="22"/>
     </row>
   </sheetData>
   <dataValidations count="9">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7" xr:uid="{ACE05F1D-CAE5-4EDA-A504-3E8FC4C61FB0}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O18" xr:uid="{A8AF5A23-2868-43A1-817E-77383D5B6152}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7" xr:uid="{ACE05F1D-CAE5-4EDA-A504-3E8FC4C61FB0}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P18" xr:uid="{A8AF5A23-2868-43A1-817E-77383D5B6152}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q18" xr:uid="{E2D5F83B-A520-43AF-A3C6-F3404E725969}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R18" xr:uid="{E2D5F83B-A520-43AF-A3C6-F3404E725969}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R18" xr:uid="{CE804842-2534-4910-9E52-7BE39EBC269B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S18" xr:uid="{CE804842-2534-4910-9E52-7BE39EBC269B}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P18" xr:uid="{3F88AA9E-5941-46B4-A570-8518956073F0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q18" xr:uid="{3F88AA9E-5941-46B4-A570-8518956073F0}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V18" xr:uid="{67BD2087-85B1-45D4-8515-6C8B49E76338}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W18" xr:uid="{67BD2087-85B1-45D4-8515-6C8B49E76338}">
       <formula1>"National, Regional, City, Community"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T18" xr:uid="{AAE7564E-286D-49C5-A759-48811FB4B64F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U18" xr:uid="{AAE7564E-286D-49C5-A759-48811FB4B64F}">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S18" xr:uid="{2C0841D1-58A9-4997-BF34-ABE3C3E0980F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T18" xr:uid="{2C0841D1-58A9-4997-BF34-ABE3C3E0980F}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U18" xr:uid="{ADCEA209-AE73-45A9-B8EC-45ED196BD936}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V18" xr:uid="{ADCEA209-AE73-45A9-B8EC-45ED196BD936}">
       <formula1>"Incentives and Support, Derisking Financial Model, Business Model"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2214,6 +2282,7 @@
     <hyperlink ref="C2" r:id="rId1" xr:uid="{3D966F76-EC1C-41C6-B94A-6CA9ED00DEB0}"/>
     <hyperlink ref="C6" r:id="rId2" xr:uid="{D303CF28-328D-4826-91BC-5C3A320BC8FD}"/>
     <hyperlink ref="C12:C18" r:id="rId3" display="Realising Energy Savings and Climate Benefits of Implementing Mandatory Energy Auditing in the Republic of Mauritius " xr:uid="{DBD8418B-A01E-4414-8F7F-9264A38446EB}"/>
+    <hyperlink ref="C12" r:id="rId4" xr:uid="{44A14E4A-2112-4454-8601-B717AF96D493}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -2223,13 +2292,13 @@
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>E6 E8:E18 E3:E4</xm:sqref>
+          <xm:sqref>F6 F8:F18 F3:F4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{19374816-2473-4BB8-881D-EEB7BC32EB0F}">
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>E2</xm:sqref>
+          <xm:sqref>F2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2265,70 +2334,70 @@
         <v>3</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N1" s="39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O1" s="39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P1" s="39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q1" s="39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R1" s="39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S1" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T1" s="39"/>
     </row>
     <row r="2" spans="1:20" ht="60.75">
-      <c r="A2" s="80">
+      <c r="A2" s="90">
         <v>6486</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="D2" s="22">
         <v>5600607</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G2" s="5">
         <v>0</v>
@@ -2337,14 +2406,14 @@
         <v>0.75</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="81" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="J2" s="91" t="s">
+        <v>30</v>
       </c>
       <c r="K2" s="14"/>
-      <c r="L2" s="82" t="s">
-        <v>29</v>
+      <c r="L2" s="92" t="s">
+        <v>31</v>
       </c>
       <c r="M2" s="32"/>
       <c r="N2" s="14"/>
@@ -2356,15 +2425,15 @@
       <c r="T2" s="14"/>
     </row>
     <row r="3" spans="1:20" ht="152.25">
-      <c r="A3" s="80"/>
+      <c r="A3" s="90"/>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
       <c r="E3" s="19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3" s="21">
         <v>0</v>
@@ -2373,13 +2442,13 @@
         <v>700000</v>
       </c>
       <c r="I3" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" s="81"/>
+        <v>36</v>
+      </c>
+      <c r="J3" s="91"/>
       <c r="K3" s="14"/>
-      <c r="L3" s="82"/>
+      <c r="L3" s="92"/>
       <c r="M3" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N3" s="14"/>
       <c r="O3" s="14"/>
@@ -2390,15 +2459,15 @@
       <c r="T3" s="14"/>
     </row>
     <row r="4" spans="1:20" ht="106.5">
-      <c r="A4" s="80"/>
+      <c r="A4" s="90"/>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
       <c r="D4" s="22"/>
       <c r="E4" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G4" s="5">
         <v>0</v>
@@ -2407,11 +2476,11 @@
         <v>1</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="81"/>
+        <v>39</v>
+      </c>
+      <c r="J4" s="91"/>
       <c r="K4" s="14"/>
-      <c r="L4" s="82"/>
+      <c r="L4" s="92"/>
       <c r="M4" s="34"/>
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
@@ -2422,28 +2491,28 @@
       <c r="T4" s="14"/>
     </row>
     <row r="5" spans="1:20" ht="60.75">
-      <c r="A5" s="80"/>
+      <c r="A5" s="90"/>
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
       <c r="E5" s="6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H5" s="5">
         <v>21000</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="81"/>
+        <v>47</v>
+      </c>
+      <c r="J5" s="91"/>
       <c r="K5" s="14"/>
-      <c r="L5" s="82"/>
+      <c r="L5" s="92"/>
       <c r="M5" s="34"/>
       <c r="N5" s="14"/>
       <c r="O5" s="14"/>
@@ -2458,19 +2527,19 @@
         <v>5681</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="D6" s="22">
         <v>28210000</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G6" s="3">
         <v>252178</v>
@@ -2479,14 +2548,14 @@
         <v>441315</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" s="83" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="J6" s="93" t="s">
+        <v>53</v>
       </c>
       <c r="K6" s="14"/>
-      <c r="L6" s="80" t="s">
-        <v>29</v>
+      <c r="L6" s="90" t="s">
+        <v>31</v>
       </c>
       <c r="M6" s="34"/>
       <c r="N6" s="14"/>
@@ -2503,10 +2572,10 @@
       <c r="C7" s="22"/>
       <c r="D7" s="22"/>
       <c r="E7" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
@@ -2515,11 +2584,11 @@
         <v>196000</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="J7" s="84"/>
+        <v>56</v>
+      </c>
+      <c r="J7" s="94"/>
       <c r="K7" s="14"/>
-      <c r="L7" s="80"/>
+      <c r="L7" s="90"/>
       <c r="M7" s="34"/>
       <c r="N7" s="14"/>
       <c r="O7" s="14"/>
@@ -2535,23 +2604,23 @@
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J8" s="84"/>
+        <v>60</v>
+      </c>
+      <c r="J8" s="94"/>
       <c r="K8" s="14"/>
-      <c r="L8" s="80"/>
+      <c r="L8" s="90"/>
       <c r="M8" s="34"/>
       <c r="N8" s="14"/>
       <c r="O8" s="14"/>
@@ -2568,20 +2637,20 @@
       <c r="D9" s="22"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H9" s="2">
         <v>18</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="J9" s="84"/>
+        <v>64</v>
+      </c>
+      <c r="J9" s="94"/>
       <c r="K9" s="14"/>
-      <c r="L9" s="80"/>
+      <c r="L9" s="90"/>
       <c r="M9" s="34"/>
       <c r="N9" s="14"/>
       <c r="O9" s="14"/>
@@ -2597,21 +2666,21 @@
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
       <c r="E10" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10" s="84"/>
+        <v>67</v>
+      </c>
+      <c r="J10" s="94"/>
       <c r="K10" s="14"/>
-      <c r="L10" s="80"/>
+      <c r="L10" s="90"/>
       <c r="M10" s="35"/>
       <c r="N10" s="14"/>
       <c r="O10" s="14"/>
@@ -2627,10 +2696,10 @@
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
       <c r="E11" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2">
         <v>5</v>
@@ -2639,13 +2708,13 @@
         <v>11</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="J11" s="85"/>
+        <v>69</v>
+      </c>
+      <c r="J11" s="95"/>
       <c r="K11" s="14"/>
-      <c r="L11" s="80"/>
+      <c r="L11" s="90"/>
       <c r="M11" s="36" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N11" s="14"/>
       <c r="O11" s="14"/>
@@ -2660,19 +2729,19 @@
         <v>5509</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D12" s="22">
         <v>4532164</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G12" s="16">
         <v>4</v>
@@ -2681,15 +2750,15 @@
         <v>40</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="J12" s="83" t="s">
-        <v>28</v>
+        <v>75</v>
+      </c>
+      <c r="J12" s="93" t="s">
+        <v>30</v>
       </c>
       <c r="K12" s="14"/>
-      <c r="L12" s="80"/>
+      <c r="L12" s="90"/>
       <c r="M12" s="37" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="N12" s="14"/>
       <c r="O12" s="14"/>
@@ -2705,10 +2774,10 @@
       <c r="C13" s="28"/>
       <c r="D13" s="22"/>
       <c r="E13" s="15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G13" s="16">
         <v>0</v>
@@ -2717,13 +2786,13 @@
         <v>435</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="J13" s="84"/>
+        <v>79</v>
+      </c>
+      <c r="J13" s="94"/>
       <c r="K13" s="14"/>
-      <c r="L13" s="80"/>
+      <c r="L13" s="90"/>
       <c r="M13" s="38" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N13" s="14"/>
       <c r="O13" s="14"/>
@@ -2739,10 +2808,10 @@
       <c r="C14" s="28"/>
       <c r="D14" s="22"/>
       <c r="E14" s="15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G14" s="16">
         <v>0</v>
@@ -2751,11 +2820,11 @@
         <v>170</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="J14" s="84"/>
+        <v>81</v>
+      </c>
+      <c r="J14" s="94"/>
       <c r="K14" s="14"/>
-      <c r="L14" s="80"/>
+      <c r="L14" s="90"/>
       <c r="M14" s="32"/>
       <c r="N14" s="14"/>
       <c r="O14" s="14"/>
@@ -2771,23 +2840,23 @@
       <c r="C15" s="28"/>
       <c r="D15" s="22"/>
       <c r="E15" s="15" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G15" s="31">
         <v>31</v>
       </c>
       <c r="H15" s="31"/>
       <c r="I15" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="J15" s="84"/>
+        <v>85</v>
+      </c>
+      <c r="J15" s="94"/>
       <c r="K15" s="30">
         <v>0.33</v>
       </c>
-      <c r="L15" s="80"/>
+      <c r="L15" s="90"/>
       <c r="M15" s="32"/>
       <c r="N15" s="14"/>
       <c r="O15" s="14"/>
@@ -2803,10 +2872,10 @@
       <c r="C16" s="28"/>
       <c r="D16" s="22"/>
       <c r="E16" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G16" s="16">
         <v>0</v>
@@ -2815,11 +2884,11 @@
         <v>50</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="J16" s="84"/>
+        <v>87</v>
+      </c>
+      <c r="J16" s="94"/>
       <c r="K16" s="14"/>
-      <c r="L16" s="80"/>
+      <c r="L16" s="90"/>
       <c r="M16" s="32"/>
       <c r="N16" s="14"/>
       <c r="O16" s="14"/>
@@ -2835,10 +2904,10 @@
       <c r="C17" s="28"/>
       <c r="D17" s="22"/>
       <c r="E17" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G17" s="16">
         <v>0</v>
@@ -2847,11 +2916,11 @@
         <v>14</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="J17" s="84"/>
+        <v>89</v>
+      </c>
+      <c r="J17" s="94"/>
       <c r="K17" s="14"/>
-      <c r="L17" s="80"/>
+      <c r="L17" s="90"/>
       <c r="M17" s="32"/>
       <c r="N17" s="14"/>
       <c r="O17" s="14"/>
@@ -2867,10 +2936,10 @@
       <c r="C18" s="29"/>
       <c r="D18" s="22"/>
       <c r="E18" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G18" s="16">
         <v>108</v>
@@ -2879,11 +2948,11 @@
         <v>348</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="J18" s="85"/>
+        <v>93</v>
+      </c>
+      <c r="J18" s="95"/>
       <c r="K18" s="14"/>
-      <c r="L18" s="80"/>
+      <c r="L18" s="90"/>
       <c r="M18" s="32"/>
       <c r="N18" s="14"/>
       <c r="O18" s="14"/>
@@ -2954,70 +3023,70 @@
         <v>3</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N1" s="39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O1" s="39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P1" s="39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q1" s="39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R1" s="39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S1" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T1" s="39"/>
     </row>
     <row r="2" spans="1:20" ht="60.75">
-      <c r="A2" s="80">
+      <c r="A2" s="90">
         <v>6486</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="D2" s="22">
         <v>5600607</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G2" s="5">
         <v>0</v>
@@ -3026,14 +3095,14 @@
         <v>0.75</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="81" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="J2" s="91" t="s">
+        <v>30</v>
       </c>
       <c r="K2" s="14"/>
-      <c r="L2" s="82" t="s">
-        <v>29</v>
+      <c r="L2" s="92" t="s">
+        <v>31</v>
       </c>
       <c r="M2" s="32"/>
       <c r="N2" s="14"/>
@@ -3045,15 +3114,15 @@
       <c r="T2" s="14"/>
     </row>
     <row r="3" spans="1:20" ht="152.25">
-      <c r="A3" s="80"/>
+      <c r="A3" s="90"/>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
       <c r="E3" s="19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3" s="21">
         <v>0</v>
@@ -3062,13 +3131,13 @@
         <v>700000</v>
       </c>
       <c r="I3" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" s="81"/>
+        <v>36</v>
+      </c>
+      <c r="J3" s="91"/>
       <c r="K3" s="14"/>
-      <c r="L3" s="82"/>
+      <c r="L3" s="92"/>
       <c r="M3" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N3" s="14"/>
       <c r="O3" s="14"/>
@@ -3079,15 +3148,15 @@
       <c r="T3" s="14"/>
     </row>
     <row r="4" spans="1:20" ht="106.5">
-      <c r="A4" s="80"/>
+      <c r="A4" s="90"/>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
       <c r="D4" s="22"/>
       <c r="E4" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G4" s="5">
         <v>0</v>
@@ -3096,11 +3165,11 @@
         <v>1</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="81"/>
+        <v>39</v>
+      </c>
+      <c r="J4" s="91"/>
       <c r="K4" s="14"/>
-      <c r="L4" s="82"/>
+      <c r="L4" s="92"/>
       <c r="M4" s="34"/>
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
@@ -3111,28 +3180,28 @@
       <c r="T4" s="14"/>
     </row>
     <row r="5" spans="1:20" ht="60.75">
-      <c r="A5" s="80"/>
+      <c r="A5" s="90"/>
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
       <c r="E5" s="6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H5" s="5">
         <v>21000</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="81"/>
+        <v>47</v>
+      </c>
+      <c r="J5" s="91"/>
       <c r="K5" s="14"/>
-      <c r="L5" s="82"/>
+      <c r="L5" s="92"/>
       <c r="M5" s="34"/>
       <c r="N5" s="14"/>
       <c r="O5" s="14"/>
@@ -3147,19 +3216,19 @@
         <v>5681</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="D6" s="22">
         <v>28210000</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G6" s="3">
         <v>252178</v>
@@ -3168,14 +3237,14 @@
         <v>441315</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" s="83" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="J6" s="93" t="s">
+        <v>53</v>
       </c>
       <c r="K6" s="14"/>
-      <c r="L6" s="80" t="s">
-        <v>29</v>
+      <c r="L6" s="90" t="s">
+        <v>31</v>
       </c>
       <c r="M6" s="34"/>
       <c r="N6" s="14"/>
@@ -3192,10 +3261,10 @@
       <c r="C7" s="22"/>
       <c r="D7" s="22"/>
       <c r="E7" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
@@ -3204,11 +3273,11 @@
         <v>196000</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="J7" s="84"/>
+        <v>56</v>
+      </c>
+      <c r="J7" s="94"/>
       <c r="K7" s="14"/>
-      <c r="L7" s="80"/>
+      <c r="L7" s="90"/>
       <c r="M7" s="34"/>
       <c r="N7" s="14"/>
       <c r="O7" s="14"/>
@@ -3224,23 +3293,23 @@
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J8" s="84"/>
+        <v>60</v>
+      </c>
+      <c r="J8" s="94"/>
       <c r="K8" s="14"/>
-      <c r="L8" s="80"/>
+      <c r="L8" s="90"/>
       <c r="M8" s="34"/>
       <c r="N8" s="14"/>
       <c r="O8" s="14"/>
@@ -3257,20 +3326,20 @@
       <c r="D9" s="22"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H9" s="2">
         <v>18</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="J9" s="84"/>
+        <v>64</v>
+      </c>
+      <c r="J9" s="94"/>
       <c r="K9" s="14"/>
-      <c r="L9" s="80"/>
+      <c r="L9" s="90"/>
       <c r="M9" s="34"/>
       <c r="N9" s="14"/>
       <c r="O9" s="14"/>
@@ -3286,21 +3355,21 @@
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
       <c r="E10" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10" s="84"/>
+        <v>67</v>
+      </c>
+      <c r="J10" s="94"/>
       <c r="K10" s="14"/>
-      <c r="L10" s="80"/>
+      <c r="L10" s="90"/>
       <c r="M10" s="35"/>
       <c r="N10" s="14"/>
       <c r="O10" s="14"/>
@@ -3316,10 +3385,10 @@
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
       <c r="E11" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2">
         <v>5</v>
@@ -3328,13 +3397,13 @@
         <v>11</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="J11" s="85"/>
+        <v>69</v>
+      </c>
+      <c r="J11" s="95"/>
       <c r="K11" s="14"/>
-      <c r="L11" s="80"/>
+      <c r="L11" s="90"/>
       <c r="M11" s="36" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N11" s="14"/>
       <c r="O11" s="14"/>
@@ -3349,19 +3418,19 @@
         <v>5509</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D12" s="22">
         <v>4532164</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G12" s="16">
         <v>4</v>
@@ -3370,15 +3439,15 @@
         <v>40</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="J12" s="83" t="s">
-        <v>28</v>
+        <v>75</v>
+      </c>
+      <c r="J12" s="93" t="s">
+        <v>30</v>
       </c>
       <c r="K12" s="14"/>
-      <c r="L12" s="80"/>
+      <c r="L12" s="90"/>
       <c r="M12" s="37" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="N12" s="14"/>
       <c r="O12" s="14"/>
@@ -3394,10 +3463,10 @@
       <c r="C13" s="28"/>
       <c r="D13" s="22"/>
       <c r="E13" s="15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G13" s="16">
         <v>0</v>
@@ -3406,13 +3475,13 @@
         <v>435</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="J13" s="84"/>
+        <v>79</v>
+      </c>
+      <c r="J13" s="94"/>
       <c r="K13" s="14"/>
-      <c r="L13" s="80"/>
+      <c r="L13" s="90"/>
       <c r="M13" s="38" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N13" s="14"/>
       <c r="O13" s="14"/>
@@ -3428,10 +3497,10 @@
       <c r="C14" s="28"/>
       <c r="D14" s="22"/>
       <c r="E14" s="15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G14" s="16">
         <v>0</v>
@@ -3440,11 +3509,11 @@
         <v>170</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="J14" s="84"/>
+        <v>81</v>
+      </c>
+      <c r="J14" s="94"/>
       <c r="K14" s="14"/>
-      <c r="L14" s="80"/>
+      <c r="L14" s="90"/>
       <c r="M14" s="32"/>
       <c r="N14" s="14"/>
       <c r="O14" s="14"/>
@@ -3460,23 +3529,23 @@
       <c r="C15" s="28"/>
       <c r="D15" s="22"/>
       <c r="E15" s="15" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G15" s="31">
         <v>31</v>
       </c>
       <c r="H15" s="31"/>
       <c r="I15" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="J15" s="84"/>
+        <v>85</v>
+      </c>
+      <c r="J15" s="94"/>
       <c r="K15" s="30">
         <v>0.33</v>
       </c>
-      <c r="L15" s="80"/>
+      <c r="L15" s="90"/>
       <c r="M15" s="32"/>
       <c r="N15" s="14"/>
       <c r="O15" s="14"/>
@@ -3492,10 +3561,10 @@
       <c r="C16" s="28"/>
       <c r="D16" s="22"/>
       <c r="E16" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G16" s="16">
         <v>0</v>
@@ -3504,11 +3573,11 @@
         <v>50</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="J16" s="84"/>
+        <v>87</v>
+      </c>
+      <c r="J16" s="94"/>
       <c r="K16" s="14"/>
-      <c r="L16" s="80"/>
+      <c r="L16" s="90"/>
       <c r="M16" s="32"/>
       <c r="N16" s="14"/>
       <c r="O16" s="14"/>
@@ -3524,10 +3593,10 @@
       <c r="C17" s="28"/>
       <c r="D17" s="22"/>
       <c r="E17" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G17" s="16">
         <v>0</v>
@@ -3536,11 +3605,11 @@
         <v>14</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="J17" s="84"/>
+        <v>89</v>
+      </c>
+      <c r="J17" s="94"/>
       <c r="K17" s="14"/>
-      <c r="L17" s="80"/>
+      <c r="L17" s="90"/>
       <c r="M17" s="32"/>
       <c r="N17" s="14"/>
       <c r="O17" s="14"/>
@@ -3556,10 +3625,10 @@
       <c r="C18" s="29"/>
       <c r="D18" s="22"/>
       <c r="E18" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G18" s="16">
         <v>108</v>
@@ -3568,11 +3637,11 @@
         <v>348</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="J18" s="85"/>
+        <v>93</v>
+      </c>
+      <c r="J18" s="95"/>
       <c r="K18" s="14"/>
-      <c r="L18" s="80"/>
+      <c r="L18" s="90"/>
       <c r="M18" s="32"/>
       <c r="N18" s="14"/>
       <c r="O18" s="14"/>
@@ -3624,179 +3693,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="87" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="87" t="s">
+      <c r="A1" s="80" t="s">
         <v>5</v>
       </c>
+      <c r="B1" s="80" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="88" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="89" t="s">
-        <v>93</v>
+      <c r="A2" s="96" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="81" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="88" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="89" t="s">
-        <v>94</v>
+      <c r="A3" s="96" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="81" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="88" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="89" t="s">
-        <v>96</v>
+      <c r="A4" s="96" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="81" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="88" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="89" t="s">
-        <v>98</v>
+      <c r="A5" s="96" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" s="81" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="88" t="s">
-        <v>99</v>
-      </c>
-      <c r="B6" s="89" t="s">
-        <v>100</v>
+      <c r="A6" s="96" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="81" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="88" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="89" t="s">
-        <v>102</v>
+      <c r="A7" s="96" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="81" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="88" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="89" t="s">
-        <v>104</v>
+      <c r="A8" s="96" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="81" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="88" t="s">
-        <v>105</v>
-      </c>
-      <c r="B9" s="89" t="s">
-        <v>106</v>
+      <c r="A9" s="96" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" s="81" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="90" t="s">
-        <v>107</v>
+      <c r="A10" s="96" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="97" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="88" t="s">
-        <v>108</v>
-      </c>
-      <c r="B11" s="90" t="s">
-        <v>109</v>
+      <c r="A11" s="96" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="97" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="88" t="s">
-        <v>110</v>
-      </c>
-      <c r="B12" s="89" t="s">
-        <v>111</v>
+      <c r="A12" s="96" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="81" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="88" t="s">
-        <v>112</v>
-      </c>
-      <c r="B13" s="90" t="s">
-        <v>113</v>
+      <c r="A13" s="96" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="97" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="88" t="s">
-        <v>114</v>
-      </c>
-      <c r="B14" s="90" t="s">
-        <v>115</v>
+      <c r="A14" s="96" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="97" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="88" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="90" t="s">
-        <v>116</v>
+      <c r="A15" s="96" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="97" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="88" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" s="90" t="s">
-        <v>117</v>
+      <c r="A16" s="96" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="97" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="88" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" s="89" t="s">
-        <v>118</v>
+      <c r="A17" s="96" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="81" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="88" t="s">
-        <v>119</v>
-      </c>
-      <c r="B18" s="90" t="s">
-        <v>120</v>
+      <c r="A18" s="96" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="97" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="88" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="90" t="s">
-        <v>121</v>
+      <c r="A19" s="96" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="97" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="88" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="90" t="s">
-        <v>122</v>
+      <c r="A20" s="96" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="97" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="88" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="91" t="s">
-        <v>123</v>
+      <c r="A21" s="96" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="98" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="88" t="s">
-        <v>124</v>
-      </c>
-      <c r="B22" s="90" t="s">
-        <v>125</v>
+      <c r="A22" s="96" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" s="97" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/01_Input/00_CO Validation/Mauritius - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Mauritius - Energy Projects.xlsx
@@ -332,7 +332,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -616,9 +616,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -704,6 +701,26 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="L19" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="M19" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2294,15 +2311,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="L19" s="68" t="n">
+      <c r="L19" s="101" t="n">
         <v>0</v>
       </c>
       <c r="M19" s="101" t="n"/>
-      <c r="N19" s="102" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="N19" s="72" t="n"/>
       <c r="O19" s="59" t="n"/>
       <c r="P19" s="73" t="n"/>
       <c r="Q19" s="92" t="n"/>
@@ -2319,7 +2332,7 @@
       <c r="AB19" s="92" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="F7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1"/>
     <dataValidation sqref="P2:P18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
@@ -2348,12 +2361,6 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
@@ -2361,6 +2368,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2539,7 +2547,7 @@
       <c r="T2" s="14" t="n"/>
     </row>
     <row r="3" ht="152.25" customHeight="1">
-      <c r="A3" s="103" t="n"/>
+      <c r="A3" s="102" t="n"/>
       <c r="B3" s="92" t="n"/>
       <c r="C3" s="92" t="n"/>
       <c r="D3" s="92" t="n"/>
@@ -2564,9 +2572,9 @@
           <t xml:space="preserve">Includes (i) Number of multi-channel mass media, social media and PIS promotional/advertising campaigns designed and executed on benefits of electric/low-carbon public transport;  (ii) Number of targeted promotional events (town-level or community-level such as apartment complexes or at major events/fairs) executed; (iii) held at MetroExpress stations or bus stations, or schools or corporate offices designed and executed; (iv) targeted campaigns on women’s safety and comfort features on public transport buses. </t>
         </is>
       </c>
-      <c r="J3" s="103" t="n"/>
+      <c r="J3" s="102" t="n"/>
       <c r="K3" s="14" t="n"/>
-      <c r="L3" s="103" t="n"/>
+      <c r="L3" s="102" t="n"/>
       <c r="M3" s="33" t="inlineStr">
         <is>
           <t>to the CO: Please estimate number of beneficiaries.
@@ -2582,7 +2590,7 @@
       <c r="T3" s="14" t="n"/>
     </row>
     <row r="4" ht="106.5" customHeight="1">
-      <c r="A4" s="103" t="n"/>
+      <c r="A4" s="102" t="n"/>
       <c r="B4" s="92" t="n"/>
       <c r="C4" s="92" t="n"/>
       <c r="D4" s="92" t="n"/>
@@ -2607,9 +2615,9 @@
           <t>Approved Gender-responsive Policy and Regulatory Framework documents endorsed and approved by the Cabinet/Parliament</t>
         </is>
       </c>
-      <c r="J4" s="103" t="n"/>
+      <c r="J4" s="102" t="n"/>
       <c r="K4" s="14" t="n"/>
-      <c r="L4" s="103" t="n"/>
+      <c r="L4" s="102" t="n"/>
       <c r="M4" s="34" t="n"/>
       <c r="N4" s="14" t="n"/>
       <c r="O4" s="14" t="n"/>
@@ -2620,7 +2628,7 @@
       <c r="T4" s="14" t="n"/>
     </row>
     <row r="5" ht="60.75" customHeight="1">
-      <c r="A5" s="104" t="n"/>
+      <c r="A5" s="103" t="n"/>
       <c r="B5" s="92" t="n"/>
       <c r="C5" s="92" t="n"/>
       <c r="D5" s="92" t="n"/>
@@ -2647,9 +2655,9 @@
           <t>Number of public transport passengers impacted in terms of number of public transport passengers that are able to travel on electric public transport buses on a regular basis</t>
         </is>
       </c>
-      <c r="J5" s="104" t="n"/>
+      <c r="J5" s="103" t="n"/>
       <c r="K5" s="14" t="n"/>
-      <c r="L5" s="104" t="n"/>
+      <c r="L5" s="103" t="n"/>
       <c r="M5" s="34" t="n"/>
       <c r="N5" s="14" t="n"/>
       <c r="O5" s="14" t="n"/>
@@ -2745,9 +2753,9 @@
 As at date, the targeted grid apsorption capacity has been acheieve (i.e., 185 MW). Phase 1 of the project is completed. The necessary regulatory framework to enhance adoption of Renewable energy is in place. the Project is now in Phase 2 which involves deployment of 25 MW solar PV panels.</t>
         </is>
       </c>
-      <c r="J7" s="103" t="n"/>
+      <c r="J7" s="102" t="n"/>
       <c r="K7" s="14" t="n"/>
-      <c r="L7" s="103" t="n"/>
+      <c r="L7" s="102" t="n"/>
       <c r="M7" s="34" t="n"/>
       <c r="N7" s="14" t="n"/>
       <c r="O7" s="14" t="n"/>
@@ -2788,9 +2796,9 @@
 Installation of rooftopps solar PV panels in households is ongoing. </t>
         </is>
       </c>
-      <c r="J8" s="103" t="n"/>
+      <c r="J8" s="102" t="n"/>
       <c r="K8" s="14" t="n"/>
-      <c r="L8" s="103" t="n"/>
+      <c r="L8" s="102" t="n"/>
       <c r="M8" s="34" t="n"/>
       <c r="N8" s="14" t="n"/>
       <c r="O8" s="14" t="n"/>
@@ -2826,9 +2834,9 @@
           <t>As at date, 18 MW total capacity of battery energy storage system has already been installed and the grid absorption capacity has been increased from 60MW to 185 MW.</t>
         </is>
       </c>
-      <c r="J9" s="103" t="n"/>
+      <c r="J9" s="102" t="n"/>
       <c r="K9" s="14" t="n"/>
-      <c r="L9" s="103" t="n"/>
+      <c r="L9" s="102" t="n"/>
       <c r="M9" s="34" t="n"/>
       <c r="N9" s="14" t="n"/>
       <c r="O9" s="14" t="n"/>
@@ -2864,9 +2872,9 @@
           <t>Government is fully supporting the project and is maintaining policy of promoting renewable energy. As a result, the Mauritius Renewable Energy Agency (MARENA) is in place and is functioning under the aegis of the Ministry of Energy and Public Utilities.</t>
         </is>
       </c>
-      <c r="J10" s="103" t="n"/>
+      <c r="J10" s="102" t="n"/>
       <c r="K10" s="14" t="n"/>
-      <c r="L10" s="103" t="n"/>
+      <c r="L10" s="102" t="n"/>
       <c r="M10" s="35" t="n"/>
       <c r="N10" s="14" t="n"/>
       <c r="O10" s="14" t="n"/>
@@ -2905,9 +2913,9 @@
 5MW PV under phases 1,2 and 3</t>
         </is>
       </c>
-      <c r="J11" s="104" t="n"/>
+      <c r="J11" s="103" t="n"/>
       <c r="K11" s="14" t="n"/>
-      <c r="L11" s="103" t="n"/>
+      <c r="L11" s="102" t="n"/>
       <c r="M11" s="36" t="inlineStr">
         <is>
           <t>to the CO: Are the 25MW discussed in this output overlapping with the # of beneficiaries listed above?
@@ -2966,7 +2974,7 @@
         </is>
       </c>
       <c r="K12" s="14" t="n"/>
-      <c r="L12" s="103" t="n"/>
+      <c r="L12" s="102" t="n"/>
       <c r="M12" s="37" t="inlineStr">
         <is>
           <t>to the CO: What is the project ID / title here?
@@ -3012,9 +3020,9 @@
           <t xml:space="preserve">Firms receiving energy-efficiency training and other support.  </t>
         </is>
       </c>
-      <c r="J13" s="103" t="n"/>
+      <c r="J13" s="102" t="n"/>
       <c r="K13" s="14" t="n"/>
-      <c r="L13" s="103" t="n"/>
+      <c r="L13" s="102" t="n"/>
       <c r="M13" s="38" t="inlineStr">
         <is>
           <t>Project Title and ID inserted. Note that the Prodoc is undergoing amendments prior to re-submission to GEF</t>
@@ -3058,9 +3066,9 @@
           <t xml:space="preserve">“Individuals” here refers to practicing and aspiring energy-efficiency professionals receiving training and other support.  </t>
         </is>
       </c>
-      <c r="J14" s="103" t="n"/>
+      <c r="J14" s="102" t="n"/>
       <c r="K14" s="14" t="n"/>
-      <c r="L14" s="103" t="n"/>
+      <c r="L14" s="102" t="n"/>
       <c r="M14" s="32" t="n"/>
       <c r="N14" s="14" t="n"/>
       <c r="O14" s="14" t="n"/>
@@ -3098,11 +3106,11 @@
           <t>Includes Energy auditors, Energy Managers, Energy Mangement Auditors, MRV specialists (33 % women)</t>
         </is>
       </c>
-      <c r="J15" s="103" t="n"/>
+      <c r="J15" s="102" t="n"/>
       <c r="K15" s="30" t="n">
         <v>0.33</v>
       </c>
-      <c r="L15" s="103" t="n"/>
+      <c r="L15" s="102" t="n"/>
       <c r="M15" s="32" t="n"/>
       <c r="N15" s="14" t="n"/>
       <c r="O15" s="14" t="n"/>
@@ -3142,9 +3150,9 @@
           <t>Communication may include not only mass media coverage, but also e-bulletins, mailings, and other direct outreach to recipients.</t>
         </is>
       </c>
-      <c r="J16" s="103" t="n"/>
+      <c r="J16" s="102" t="n"/>
       <c r="K16" s="14" t="n"/>
-      <c r="L16" s="103" t="n"/>
+      <c r="L16" s="102" t="n"/>
       <c r="M16" s="32" t="n"/>
       <c r="N16" s="14" t="n"/>
       <c r="O16" s="14" t="n"/>
@@ -3184,9 +3192,9 @@
           <t xml:space="preserve">Includes agreement on Roadmap, achieving energy savings and GHG reductions targets, restructuring of EEMO, enery audit mandatory for private sector, new MEPS adopted, Mauritas accredited, etc. </t>
         </is>
       </c>
-      <c r="J17" s="103" t="n"/>
+      <c r="J17" s="102" t="n"/>
       <c r="K17" s="14" t="n"/>
-      <c r="L17" s="103" t="n"/>
+      <c r="L17" s="102" t="n"/>
       <c r="M17" s="32" t="n"/>
       <c r="N17" s="14" t="n"/>
       <c r="O17" s="14" t="n"/>
@@ -3226,9 +3234,9 @@
           <t>Baseline : Before the project: 108 firms as of March 2018   End of Project:  80 firms beyond baseline from among the 650 largest energy consumers, plus 160 SMEs (Additional of 240 over the baseline of 108 equals 348).</t>
         </is>
       </c>
-      <c r="J18" s="104" t="n"/>
+      <c r="J18" s="103" t="n"/>
       <c r="K18" s="14" t="n"/>
-      <c r="L18" s="104" t="n"/>
+      <c r="L18" s="103" t="n"/>
       <c r="M18" s="32" t="n"/>
       <c r="N18" s="14" t="n"/>
       <c r="O18" s="14" t="n"/>
@@ -3440,7 +3448,7 @@
       <c r="T2" s="14" t="n"/>
     </row>
     <row r="3" ht="152.25" customHeight="1">
-      <c r="A3" s="103" t="n"/>
+      <c r="A3" s="102" t="n"/>
       <c r="B3" s="92" t="n"/>
       <c r="C3" s="92" t="n"/>
       <c r="D3" s="92" t="n"/>
@@ -3465,9 +3473,9 @@
           <t xml:space="preserve">Includes (i) Number of multi-channel mass media, social media and PIS promotional/advertising campaigns designed and executed on benefits of electric/low-carbon public transport;  (ii) Number of targeted promotional events (town-level or community-level such as apartment complexes or at major events/fairs) executed; (iii) held at MetroExpress stations or bus stations, or schools or corporate offices designed and executed; (iv) targeted campaigns on women’s safety and comfort features on public transport buses. </t>
         </is>
       </c>
-      <c r="J3" s="103" t="n"/>
+      <c r="J3" s="102" t="n"/>
       <c r="K3" s="14" t="n"/>
-      <c r="L3" s="103" t="n"/>
+      <c r="L3" s="102" t="n"/>
       <c r="M3" s="33" t="inlineStr">
         <is>
           <t>to the CO: Please estimate number of beneficiaries.
@@ -3483,7 +3491,7 @@
       <c r="T3" s="14" t="n"/>
     </row>
     <row r="4" ht="106.5" customHeight="1">
-      <c r="A4" s="103" t="n"/>
+      <c r="A4" s="102" t="n"/>
       <c r="B4" s="92" t="n"/>
       <c r="C4" s="92" t="n"/>
       <c r="D4" s="92" t="n"/>
@@ -3508,9 +3516,9 @@
           <t>Approved Gender-responsive Policy and Regulatory Framework documents endorsed and approved by the Cabinet/Parliament</t>
         </is>
       </c>
-      <c r="J4" s="103" t="n"/>
+      <c r="J4" s="102" t="n"/>
       <c r="K4" s="14" t="n"/>
-      <c r="L4" s="103" t="n"/>
+      <c r="L4" s="102" t="n"/>
       <c r="M4" s="34" t="n"/>
       <c r="N4" s="14" t="n"/>
       <c r="O4" s="14" t="n"/>
@@ -3521,7 +3529,7 @@
       <c r="T4" s="14" t="n"/>
     </row>
     <row r="5" ht="60.75" customHeight="1">
-      <c r="A5" s="104" t="n"/>
+      <c r="A5" s="103" t="n"/>
       <c r="B5" s="92" t="n"/>
       <c r="C5" s="92" t="n"/>
       <c r="D5" s="92" t="n"/>
@@ -3548,9 +3556,9 @@
           <t>Number of public transport passengers impacted in terms of number of public transport passengers that are able to travel on electric public transport buses on a regular basis</t>
         </is>
       </c>
-      <c r="J5" s="104" t="n"/>
+      <c r="J5" s="103" t="n"/>
       <c r="K5" s="14" t="n"/>
-      <c r="L5" s="104" t="n"/>
+      <c r="L5" s="103" t="n"/>
       <c r="M5" s="34" t="n"/>
       <c r="N5" s="14" t="n"/>
       <c r="O5" s="14" t="n"/>
@@ -3646,9 +3654,9 @@
 As at date, the targeted grid apsorption capacity has been acheieve (i.e., 185 MW). Phase 1 of the project is completed. The necessary regulatory framework to enhance adoption of Renewable energy is in place. the Project is now in Phase 2 which involves deployment of 25 MW solar PV panels.</t>
         </is>
       </c>
-      <c r="J7" s="103" t="n"/>
+      <c r="J7" s="102" t="n"/>
       <c r="K7" s="14" t="n"/>
-      <c r="L7" s="103" t="n"/>
+      <c r="L7" s="102" t="n"/>
       <c r="M7" s="34" t="n"/>
       <c r="N7" s="14" t="n"/>
       <c r="O7" s="14" t="n"/>
@@ -3689,9 +3697,9 @@
 Installation of rooftopps solar PV panels in households is ongoing. </t>
         </is>
       </c>
-      <c r="J8" s="103" t="n"/>
+      <c r="J8" s="102" t="n"/>
       <c r="K8" s="14" t="n"/>
-      <c r="L8" s="103" t="n"/>
+      <c r="L8" s="102" t="n"/>
       <c r="M8" s="34" t="n"/>
       <c r="N8" s="14" t="n"/>
       <c r="O8" s="14" t="n"/>
@@ -3727,9 +3735,9 @@
           <t>As at date, 18 MW total capacity of battery energy storage system has already been installed and the grid absorption capacity has been increased from 60MW to 185 MW.</t>
         </is>
       </c>
-      <c r="J9" s="103" t="n"/>
+      <c r="J9" s="102" t="n"/>
       <c r="K9" s="14" t="n"/>
-      <c r="L9" s="103" t="n"/>
+      <c r="L9" s="102" t="n"/>
       <c r="M9" s="34" t="n"/>
       <c r="N9" s="14" t="n"/>
       <c r="O9" s="14" t="n"/>
@@ -3765,9 +3773,9 @@
           <t>Government is fully supporting the project and is maintaining policy of promoting renewable energy. As a result, the Mauritius Renewable Energy Agency (MARENA) is in place and is functioning under the aegis of the Ministry of Energy and Public Utilities.</t>
         </is>
       </c>
-      <c r="J10" s="103" t="n"/>
+      <c r="J10" s="102" t="n"/>
       <c r="K10" s="14" t="n"/>
-      <c r="L10" s="103" t="n"/>
+      <c r="L10" s="102" t="n"/>
       <c r="M10" s="35" t="n"/>
       <c r="N10" s="14" t="n"/>
       <c r="O10" s="14" t="n"/>
@@ -3806,9 +3814,9 @@
 5MW PV under phases 1,2 and 3</t>
         </is>
       </c>
-      <c r="J11" s="104" t="n"/>
+      <c r="J11" s="103" t="n"/>
       <c r="K11" s="14" t="n"/>
-      <c r="L11" s="103" t="n"/>
+      <c r="L11" s="102" t="n"/>
       <c r="M11" s="36" t="inlineStr">
         <is>
           <t>to the CO: Are the 25MW discussed in this output overlapping with the # of beneficiaries listed above?
@@ -3867,7 +3875,7 @@
         </is>
       </c>
       <c r="K12" s="14" t="n"/>
-      <c r="L12" s="103" t="n"/>
+      <c r="L12" s="102" t="n"/>
       <c r="M12" s="37" t="inlineStr">
         <is>
           <t>to the CO: What is the project ID / title here?
@@ -3913,9 +3921,9 @@
           <t xml:space="preserve">Firms receiving energy-efficiency training and other support.  </t>
         </is>
       </c>
-      <c r="J13" s="103" t="n"/>
+      <c r="J13" s="102" t="n"/>
       <c r="K13" s="14" t="n"/>
-      <c r="L13" s="103" t="n"/>
+      <c r="L13" s="102" t="n"/>
       <c r="M13" s="38" t="inlineStr">
         <is>
           <t>Project Title and ID inserted. Note that the Prodoc is undergoing amendments prior to re-submission to GEF</t>
@@ -3959,9 +3967,9 @@
           <t xml:space="preserve">“Individuals” here refers to practicing and aspiring energy-efficiency professionals receiving training and other support.  </t>
         </is>
       </c>
-      <c r="J14" s="103" t="n"/>
+      <c r="J14" s="102" t="n"/>
       <c r="K14" s="14" t="n"/>
-      <c r="L14" s="103" t="n"/>
+      <c r="L14" s="102" t="n"/>
       <c r="M14" s="32" t="n"/>
       <c r="N14" s="14" t="n"/>
       <c r="O14" s="14" t="n"/>
@@ -3999,11 +4007,11 @@
           <t>Includes Energy auditors, Energy Managers, Energy Mangement Auditors, MRV specialists (33 % women)</t>
         </is>
       </c>
-      <c r="J15" s="103" t="n"/>
+      <c r="J15" s="102" t="n"/>
       <c r="K15" s="30" t="n">
         <v>0.33</v>
       </c>
-      <c r="L15" s="103" t="n"/>
+      <c r="L15" s="102" t="n"/>
       <c r="M15" s="32" t="n"/>
       <c r="N15" s="14" t="n"/>
       <c r="O15" s="14" t="n"/>
@@ -4043,9 +4051,9 @@
           <t>Communication may include not only mass media coverage, but also e-bulletins, mailings, and other direct outreach to recipients.</t>
         </is>
       </c>
-      <c r="J16" s="103" t="n"/>
+      <c r="J16" s="102" t="n"/>
       <c r="K16" s="14" t="n"/>
-      <c r="L16" s="103" t="n"/>
+      <c r="L16" s="102" t="n"/>
       <c r="M16" s="32" t="n"/>
       <c r="N16" s="14" t="n"/>
       <c r="O16" s="14" t="n"/>
@@ -4085,9 +4093,9 @@
           <t xml:space="preserve">Includes agreement on Roadmap, achieving energy savings and GHG reductions targets, restructuring of EEMO, enery audit mandatory for private sector, new MEPS adopted, Mauritas accredited, etc. </t>
         </is>
       </c>
-      <c r="J17" s="103" t="n"/>
+      <c r="J17" s="102" t="n"/>
       <c r="K17" s="14" t="n"/>
-      <c r="L17" s="103" t="n"/>
+      <c r="L17" s="102" t="n"/>
       <c r="M17" s="32" t="n"/>
       <c r="N17" s="14" t="n"/>
       <c r="O17" s="14" t="n"/>
@@ -4127,9 +4135,9 @@
           <t>Baseline : Before the project: 108 firms as of March 2018   End of Project:  80 firms beyond baseline from among the 650 largest energy consumers, plus 160 SMEs (Additional of 240 over the baseline of 108 equals 348).</t>
         </is>
       </c>
-      <c r="J18" s="104" t="n"/>
+      <c r="J18" s="103" t="n"/>
       <c r="K18" s="14" t="n"/>
-      <c r="L18" s="104" t="n"/>
+      <c r="L18" s="103" t="n"/>
       <c r="M18" s="32" t="n"/>
       <c r="N18" s="14" t="n"/>
       <c r="O18" s="14" t="n"/>
@@ -4180,288 +4188,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="105" t="inlineStr">
+      <c r="A1" s="104" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="105" t="inlineStr">
+      <c r="B1" s="104" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="45.75" customHeight="1">
-      <c r="A2" s="106" t="inlineStr">
+      <c r="A2" s="105" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="106" t="inlineStr">
+      <c r="B2" s="105" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="106" t="inlineStr">
+      <c r="A3" s="105" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="106" t="inlineStr">
+      <c r="B3" s="105" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1">
-      <c r="A4" s="106" t="inlineStr">
+      <c r="A4" s="105" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="106" t="inlineStr">
+      <c r="B4" s="105" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30.75" customHeight="1">
-      <c r="A5" s="106" t="inlineStr">
+      <c r="A5" s="105" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="106" t="inlineStr">
+      <c r="B5" s="105" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
-      <c r="A6" s="106" t="inlineStr">
+      <c r="A6" s="105" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="106" t="inlineStr">
+      <c r="B6" s="105" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45.75" customHeight="1">
-      <c r="A7" s="106" t="inlineStr">
+      <c r="A7" s="105" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="106" t="inlineStr">
+      <c r="B7" s="105" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45.75" customHeight="1">
-      <c r="A8" s="106" t="inlineStr">
+      <c r="A8" s="105" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="106" t="inlineStr">
+      <c r="B8" s="105" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1">
-      <c r="A9" s="106" t="inlineStr">
+      <c r="A9" s="105" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="106" t="inlineStr">
+      <c r="B9" s="105" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="106" t="inlineStr">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="106" t="inlineStr">
+      <c r="B10" s="105" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="106" t="inlineStr">
+      <c r="A11" s="105" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="106" t="inlineStr">
+      <c r="B11" s="105" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45.75" customHeight="1">
-      <c r="A12" s="106" t="inlineStr">
+      <c r="A12" s="105" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="106" t="inlineStr">
+      <c r="B12" s="105" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="106" t="inlineStr">
+      <c r="A13" s="105" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="106" t="inlineStr">
+      <c r="B13" s="105" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="106" t="inlineStr">
+      <c r="A14" s="105" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="106" t="inlineStr">
+      <c r="B14" s="105" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30.75" customHeight="1">
-      <c r="A15" s="106" t="inlineStr">
+      <c r="A15" s="105" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="106" t="inlineStr">
+      <c r="B15" s="105" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30.75" customHeight="1">
-      <c r="A16" s="106" t="inlineStr">
+      <c r="A16" s="105" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="106" t="inlineStr">
+      <c r="B16" s="105" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30.75" customHeight="1">
-      <c r="A17" s="106" t="inlineStr">
+      <c r="A17" s="105" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="106" t="inlineStr">
+      <c r="B17" s="105" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30.75" customHeight="1">
-      <c r="A18" s="106" t="inlineStr">
+      <c r="A18" s="105" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="106" t="inlineStr">
+      <c r="B18" s="105" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="76.5" customHeight="1">
-      <c r="A19" s="106" t="inlineStr">
+      <c r="A19" s="105" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="106" t="inlineStr">
+      <c r="B19" s="105" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30.75" customHeight="1">
-      <c r="A20" s="106" t="inlineStr">
+      <c r="A20" s="105" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="106" t="inlineStr">
+      <c r="B20" s="105" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45.75" customHeight="1">
-      <c r="A21" s="106" t="inlineStr">
+      <c r="A21" s="105" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="106" t="inlineStr">
+      <c r="B21" s="105" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30.75" customHeight="1">
-      <c r="A22" s="106" t="inlineStr">
+      <c r="A22" s="105" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="106" t="inlineStr">
+      <c r="B22" s="105" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="106" t="inlineStr">
+      <c r="A23" s="105" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="106" t="inlineStr">
+      <c r="B23" s="105" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="106" t="inlineStr">
+      <c r="A24" s="105" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="106" t="inlineStr">
+      <c r="B24" s="105" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
